--- a/data/Brightspeed_Scenario2_App_Data_Jan_Sep_2026.xlsx
+++ b/data/Brightspeed_Scenario2_App_Data_Jan_Sep_2026.xlsx
@@ -2,17 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard KPI" sheetId="1" r:id="R71dff1aba6754f89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Overview" sheetId="2" r:id="R9c015622a7eb4d73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Monthly" sheetId="3" r:id="Rbbbc85454021443b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="September State Drill" sheetId="4" r:id="R71199731b7604594"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ODD Timing" sheetId="5" r:id="R796d57ebe1c84d8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancel Classification" sheetId="6" r:id="R362d2c569a234abe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer Miss Reasons" sheetId="7" r:id="R7bec949243a64371"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchtower Signals" sheetId="8" r:id="Rd65edadd43984a38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example Customer Journey" sheetId="9" r:id="R6edf11bf2226452d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Questions" sheetId="10" r:id="Rb95a0542c4f74352"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="11" r:id="R786b6d43e4e14d19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard KPI" sheetId="1" r:id="Rf860294426f04525"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Overview" sheetId="2" r:id="R4b0a6e11bb8046ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State Monthly" sheetId="3" r:id="Rce06eb7917c34a5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="September State Drill" sheetId="4" r:id="R19af6201a1554009"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ODD Timing" sheetId="5" r:id="R22c31c46ec9c4a77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cancel Classification" sheetId="6" r:id="R3b27c6ac8a7a4f44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer Miss Reasons" sheetId="7" r:id="R7377c946fccd4563"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchtower Signals" sheetId="8" r:id="Rd00f4a66d1d14558"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example Customer Journey" sheetId="9" r:id="Rb42ffea8a66e4eb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Questions" sheetId="10" r:id="R0857fb65360b454d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="11" r:id="R1c7db6a9564e4520"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Channel Monthly" sheetId="12" r:id="R11d95e4f408546ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="September Channel Drill" sheetId="13" r:id="Rd1adf5ec6c3644a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="September State x Channel" sheetId="14" r:id="R9c562884bf774e4d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -80,7 +83,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="17">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -132,6 +135,36 @@
         <x:fgColor rgb="FFEAF8EF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0D0D0E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1C1C1E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF1E6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2FF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFDECEC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFC72C"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -140,7 +173,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="106">
+  <x:cellXfs count="133">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -415,6 +448,71 @@
     <x:xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="5" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="5" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="5" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="5" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -443,6 +541,7 @@
     <c:plotArea>
       <c:lineChart>
         <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -620,7 +719,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5d0607f19a2c4e66"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R278c7ab86e36481c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1544,12 +1643,193 @@
         <x:v>Leading customer-engagement signal.</x:v>
       </x:c>
     </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="132" t="str">
+        <x:v>September channel snapshot — broad deterioration, no single-channel root cause</x:v>
+      </x:c>
+      <x:c r="B41" s="132" t="str">
+        <x:v>September channel snapshot — broad deterioration, no single-channel root cause</x:v>
+      </x:c>
+      <x:c r="C41" s="132" t="str">
+        <x:v>September channel snapshot — broad deterioration, no single-channel root cause</x:v>
+      </x:c>
+      <x:c r="D41" s="132" t="str">
+        <x:v>September channel snapshot — broad deterioration, no single-channel root cause</x:v>
+      </x:c>
+      <x:c r="E41" s="132" t="str">
+        <x:v>September channel snapshot — broad deterioration, no single-channel root cause</x:v>
+      </x:c>
+      <x:c r="F41" s="132" t="str">
+        <x:v>September channel snapshot — broad deterioration, no single-channel root cause</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="116" t="str">
+        <x:v>Channel</x:v>
+      </x:c>
+      <x:c r="B42" s="116" t="str">
+        <x:v>Unique Sales</x:v>
+      </x:c>
+      <x:c r="C42" s="116" t="str">
+        <x:v>Cancellations</x:v>
+      </x:c>
+      <x:c r="D42" s="116" t="str">
+        <x:v>Cancel Rate</x:v>
+      </x:c>
+      <x:c r="E42" s="116" t="str">
+        <x:v>Cancel Growth vs Aug</x:v>
+      </x:c>
+      <x:c r="F42" s="116" t="str">
+        <x:v>Scenario interpretation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="121" t="str">
+        <x:v>D2D</x:v>
+      </x:c>
+      <x:c r="B43" s="122" t="n">
+        <x:v>7805</x:v>
+      </x:c>
+      <x:c r="C43" s="122" t="n">
+        <x:v>1516</x:v>
+      </x:c>
+      <x:c r="D43" s="123" t="n">
+        <x:v>0.194234465086483</x:v>
+      </x:c>
+      <x:c r="E43" s="123" t="n">
+        <x:v>0.31940818102698</x:v>
+      </x:c>
+      <x:c r="F43" s="121" t="str">
+        <x:v>Broad-based increase; continue to state / ODD / Customer Miss drill</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="121" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="B44" s="122" t="n">
+        <x:v>6994</x:v>
+      </x:c>
+      <x:c r="C44" s="122" t="n">
+        <x:v>1208</x:v>
+      </x:c>
+      <x:c r="D44" s="123" t="n">
+        <x:v>0.17271947383471548</x:v>
+      </x:c>
+      <x:c r="E44" s="123" t="n">
+        <x:v>0.27966101694915246</x:v>
+      </x:c>
+      <x:c r="F44" s="121" t="str">
+        <x:v>Broad-based increase; continue to state / ODD / Customer Miss drill</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="121" t="str">
+        <x:v>Digital Partner</x:v>
+      </x:c>
+      <x:c r="B45" s="122" t="n">
+        <x:v>5371</x:v>
+      </x:c>
+      <x:c r="C45" s="122" t="n">
+        <x:v>1018</x:v>
+      </x:c>
+      <x:c r="D45" s="123" t="n">
+        <x:v>0.18953639918078571</x:v>
+      </x:c>
+      <x:c r="E45" s="123" t="n">
+        <x:v>0.29024081115335876</x:v>
+      </x:c>
+      <x:c r="F45" s="121" t="str">
+        <x:v>Broad-based increase; continue to state / ODD / Customer Miss drill</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="121" t="str">
+        <x:v>Inbound</x:v>
+      </x:c>
+      <x:c r="B46" s="122" t="n">
+        <x:v>6608</x:v>
+      </x:c>
+      <x:c r="C46" s="122" t="n">
+        <x:v>1230</x:v>
+      </x:c>
+      <x:c r="D46" s="123" t="n">
+        <x:v>0.18613801452784504</x:v>
+      </x:c>
+      <x:c r="E46" s="123" t="n">
+        <x:v>0.3099041533546325</x:v>
+      </x:c>
+      <x:c r="F46" s="121" t="str">
+        <x:v>Broad-based increase; continue to state / ODD / Customer Miss drill</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="121" t="str">
+        <x:v>Indirect</x:v>
+      </x:c>
+      <x:c r="B47" s="122" t="n">
+        <x:v>4598</x:v>
+      </x:c>
+      <x:c r="C47" s="122" t="n">
+        <x:v>888</x:v>
+      </x:c>
+      <x:c r="D47" s="123" t="n">
+        <x:v>0.19312744671596346</x:v>
+      </x:c>
+      <x:c r="E47" s="123" t="n">
+        <x:v>0.30014641288433386</x:v>
+      </x:c>
+      <x:c r="F47" s="121" t="str">
+        <x:v>Broad-based increase; continue to state / ODD / Customer Miss drill</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="121" t="str">
+        <x:v>OBTM</x:v>
+      </x:c>
+      <x:c r="B48" s="122" t="n">
+        <x:v>4250</x:v>
+      </x:c>
+      <x:c r="C48" s="122" t="n">
+        <x:v>778</x:v>
+      </x:c>
+      <x:c r="D48" s="123" t="n">
+        <x:v>0.18305882352941177</x:v>
+      </x:c>
+      <x:c r="E48" s="123" t="n">
+        <x:v>0.269168026101142</x:v>
+      </x:c>
+      <x:c r="F48" s="121" t="str">
+        <x:v>Broad-based increase; continue to state / ODD / Customer Miss drill</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="121" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B49" s="122" t="n">
+        <x:v>3014</x:v>
+      </x:c>
+      <x:c r="C49" s="122" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="D49" s="123" t="n">
+        <x:v>0.19907100199071</x:v>
+      </x:c>
+      <x:c r="E49" s="123" t="n">
+        <x:v>0.33037694013303764</x:v>
+      </x:c>
+      <x:c r="F49" s="121" t="str">
+        <x:v>Broad-based increase; continue to state / ODD / Customer Miss drill</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F2"/>
     <x:mergeCell ref="A3:F3"/>
     <x:mergeCell ref="A5:F5"/>
     <x:mergeCell ref="A33:F33"/>
+    <x:mergeCell ref="A41:F41"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1695,16 +1975,16 @@
         <x:v>Which channels, partners, markets or teams are contributing most?</x:v>
       </x:c>
       <x:c r="C8" s="56" t="str">
-        <x:v>North Carolina is the clearest geographic hotspot, with cancellations up ~46% vs August and the highest Post-ODD / Pending Contact concentration.</x:v>
+        <x:v>North Carolina is the clearest geographic hotspot. Channel deterioration is broad-based, so no single sales channel explains the September shock.</x:v>
       </x:c>
       <x:c r="D8" s="56" t="str">
-        <x:v>NC: 9.5K sales, 1.9K cancels, ~19.9% cancel rate, 65% Post ODD, 42% Pending Contact.</x:v>
+        <x:v>NC: ~9.5K sales, ~1.9K cancels, ~19.9% cancel rate, 65% Post ODD and 42% Pending Customer Contact; channel cancel growth is broadly ~27–33%.</x:v>
       </x:c>
       <x:c r="E8" s="56" t="str">
-        <x:v>Prioritize NC customer rescue before broad network-wide intervention.</x:v>
+        <x:v>Prioritize North Carolina customer rescue rather than a channel-specific intervention.</x:v>
       </x:c>
       <x:c r="F8" s="56" t="str">
-        <x:v>September State Drill</x:v>
+        <x:v>September State Drill / September Channel Drill</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2056,10 +2336,6667 @@
         <x:v>Only 3% in Scenario 2 — not the main cause.</x:v>
       </x:c>
     </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="30" t="str">
+        <x:v>Channel</x:v>
+      </x:c>
+      <x:c r="B19" s="30" t="str">
+        <x:v>Brightspeed sales channel label.</x:v>
+      </x:c>
+      <x:c r="C19" s="30" t="str">
+        <x:v>Category</x:v>
+      </x:c>
+      <x:c r="D19" s="30" t="str">
+        <x:v>Channel Monthly / September Channel Drill</x:v>
+      </x:c>
+      <x:c r="E19" s="30" t="str">
+        <x:v>D2D, Digital, Digital Partner, Inbound, Indirect, OBTM, Other.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="30" t="str">
+        <x:v>Channel Unique Sales</x:v>
+      </x:c>
+      <x:c r="B20" s="30" t="str">
+        <x:v>Unique Sales attributed to a sales channel.</x:v>
+      </x:c>
+      <x:c r="C20" s="30" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="D20" s="30" t="str">
+        <x:v>Channel Monthly</x:v>
+      </x:c>
+      <x:c r="E20" s="30" t="str">
+        <x:v>Used to compare demand by source.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="30" t="str">
+        <x:v>Channel Cancellations</x:v>
+      </x:c>
+      <x:c r="B21" s="30" t="str">
+        <x:v>Cancellations attributed to a sales channel.</x:v>
+      </x:c>
+      <x:c r="C21" s="30" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="D21" s="30" t="str">
+        <x:v>Channel Monthly</x:v>
+      </x:c>
+      <x:c r="E21" s="30" t="str">
+        <x:v>September rises broadly across channels.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="30" t="str">
+        <x:v>Channel Cancel Rate</x:v>
+      </x:c>
+      <x:c r="B22" s="30" t="str">
+        <x:v>Channel Cancellations ÷ Channel Unique Sales.</x:v>
+      </x:c>
+      <x:c r="C22" s="30" t="str">
+        <x:v>%</x:v>
+      </x:c>
+      <x:c r="D22" s="30" t="str">
+        <x:v>Channel Monthly / September Channel Drill</x:v>
+      </x:c>
+      <x:c r="E22" s="30" t="str">
+        <x:v>No single channel is the root cause in Scenario 2.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="30" t="str">
+        <x:v>Channel Post-ODD %</x:v>
+      </x:c>
+      <x:c r="B23" s="30" t="str">
+        <x:v>Share of channel cancellations occurring after ODD.</x:v>
+      </x:c>
+      <x:c r="C23" s="30" t="str">
+        <x:v>%</x:v>
+      </x:c>
+      <x:c r="D23" s="30" t="str">
+        <x:v>Channel Monthly / September Channel Drill</x:v>
+      </x:c>
+      <x:c r="E23" s="30" t="str">
+        <x:v>All channels shift later in September.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="30" t="str">
+        <x:v>State × Channel</x:v>
+      </x:c>
+      <x:c r="B24" s="30" t="str">
+        <x:v>September state/channel cross-drill.</x:v>
+      </x:c>
+      <x:c r="C24" s="30" t="str">
+        <x:v>Count / %</x:v>
+      </x:c>
+      <x:c r="D24" s="30" t="str">
+        <x:v>September State x Channel</x:v>
+      </x:c>
+      <x:c r="E24" s="30" t="str">
+        <x:v>Supports state → channel exploration in the app.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E2"/>
     <x:mergeCell ref="A3:E3"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="19" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="13" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="11" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="13" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="14" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="13" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="13" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="10" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="24" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="19" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="B1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="C1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="D1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="E1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="F1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="G1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="H1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="I1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="J1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="K1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="L1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="M1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="N1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="O1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="P1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="Q1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="R1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="S1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="T1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="U1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="V1" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="27" customHeight="1">
+      <x:c r="A2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="B2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="C2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="D2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="E2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="F2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="G2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="H2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="I2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="J2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="K2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="L2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="M2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="N2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="O2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="P2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="Q2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="R2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="S2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="T2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="U2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+      <x:c r="V2" s="109" t="str">
+        <x:v>Channel-Level Monthly Data — Jan to Sep 2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="B3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="C3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="D3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="E3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="F3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="G3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="H3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="I3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="J3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="K3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="L3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="M3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="N3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="O3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="P3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="Q3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="R3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="S3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="T3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="U3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+      <x:c r="V3" s="112" t="str">
+        <x:v>All seven Brightspeed sales channels. Jan–Aug remain stable; September deterioration is broad-based, not caused by one channel.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="116" t="str">
+        <x:v>Month</x:v>
+      </x:c>
+      <x:c r="B5" s="116" t="str">
+        <x:v>Channel</x:v>
+      </x:c>
+      <x:c r="C5" s="116" t="str">
+        <x:v>Unique Sales</x:v>
+      </x:c>
+      <x:c r="D5" s="116" t="str">
+        <x:v>Installs</x:v>
+      </x:c>
+      <x:c r="E5" s="116" t="str">
+        <x:v>Cancellations</x:v>
+      </x:c>
+      <x:c r="F5" s="116" t="str">
+        <x:v>Cancel Rate</x:v>
+      </x:c>
+      <x:c r="G5" s="116" t="str">
+        <x:v>Cancels MoM %</x:v>
+      </x:c>
+      <x:c r="H5" s="116" t="str">
+        <x:v>Pre-ODD Cancels</x:v>
+      </x:c>
+      <x:c r="I5" s="116" t="str">
+        <x:v>Pre-ODD %</x:v>
+      </x:c>
+      <x:c r="J5" s="116" t="str">
+        <x:v>On-ODD Cancels</x:v>
+      </x:c>
+      <x:c r="K5" s="116" t="str">
+        <x:v>On-ODD %</x:v>
+      </x:c>
+      <x:c r="L5" s="116" t="str">
+        <x:v>Post-ODD Cancels</x:v>
+      </x:c>
+      <x:c r="M5" s="116" t="str">
+        <x:v>Post-ODD %</x:v>
+      </x:c>
+      <x:c r="N5" s="116" t="str">
+        <x:v>Customer Miss</x:v>
+      </x:c>
+      <x:c r="O5" s="116" t="str">
+        <x:v>Customer Miss %</x:v>
+      </x:c>
+      <x:c r="P5" s="116" t="str">
+        <x:v>Company Miss</x:v>
+      </x:c>
+      <x:c r="Q5" s="116" t="str">
+        <x:v>Company Miss %</x:v>
+      </x:c>
+      <x:c r="R5" s="116" t="str">
+        <x:v>Faux Cancels</x:v>
+      </x:c>
+      <x:c r="S5" s="116" t="str">
+        <x:v>Faux %</x:v>
+      </x:c>
+      <x:c r="T5" s="116" t="str">
+        <x:v>Pending Customer Contact %</x:v>
+      </x:c>
+      <x:c r="U5" s="116" t="str">
+        <x:v>Install in Jeopardy %</x:v>
+      </x:c>
+      <x:c r="V5" s="116" t="str">
+        <x:v>BSW Delay Predicted %</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="62" t="n">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="B6" s="30" t="str">
+        <x:v>D2D</x:v>
+      </x:c>
+      <x:c r="C6" s="64" t="n">
+        <x:v>6040</x:v>
+      </x:c>
+      <x:c r="D6" s="64" t="n">
+        <x:v>4899</x:v>
+      </x:c>
+      <x:c r="E6" s="64" t="n">
+        <x:v>936</x:v>
+      </x:c>
+      <x:c r="F6" s="66" t="n">
+        <x:v>0.15496688741721854</x:v>
+      </x:c>
+      <x:c r="G6" s="66"/>
+      <x:c r="H6" s="64" t="n">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="I6" s="66" t="n">
+        <x:v>0.46047008547008544</x:v>
+      </x:c>
+      <x:c r="J6" s="64" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="K6" s="66" t="n">
+        <x:v>0.10042735042735043</x:v>
+      </x:c>
+      <x:c r="L6" s="64" t="n">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="M6" s="66" t="n">
+        <x:v>0.4391025641025641</x:v>
+      </x:c>
+      <x:c r="N6" s="64" t="n">
+        <x:v>627</x:v>
+      </x:c>
+      <x:c r="O6" s="66" t="n">
+        <x:v>0.6698717948717948</x:v>
+      </x:c>
+      <x:c r="P6" s="64" t="n">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="Q6" s="66" t="n">
+        <x:v>0.2799145299145299</x:v>
+      </x:c>
+      <x:c r="R6" s="64" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="S6" s="66" t="n">
+        <x:v>0.050213675213675216</x:v>
+      </x:c>
+      <x:c r="T6" s="66" t="n">
+        <x:v>0.18000000000000002</x:v>
+      </x:c>
+      <x:c r="U6" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V6" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="62" t="n">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="B7" s="30" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="C7" s="64" t="n">
+        <x:v>5436</x:v>
+      </x:c>
+      <x:c r="D7" s="64" t="n">
+        <x:v>4634</x:v>
+      </x:c>
+      <x:c r="E7" s="64" t="n">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="F7" s="66" t="n">
+        <x:v>0.141280353200883</x:v>
+      </x:c>
+      <x:c r="G7" s="66"/>
+      <x:c r="H7" s="64" t="n">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="I7" s="66" t="n">
+        <x:v>0.48046875</x:v>
+      </x:c>
+      <x:c r="J7" s="64" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="K7" s="66" t="n">
+        <x:v>0.10026041666666667</x:v>
+      </x:c>
+      <x:c r="L7" s="64" t="n">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="M7" s="66" t="n">
+        <x:v>0.4192708333333333</x:v>
+      </x:c>
+      <x:c r="N7" s="64" t="n">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="O7" s="66" t="n">
+        <x:v>0.6497395833333334</x:v>
+      </x:c>
+      <x:c r="P7" s="64" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="Q7" s="66" t="n">
+        <x:v>0.2994791666666667</x:v>
+      </x:c>
+      <x:c r="R7" s="64" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="S7" s="66" t="n">
+        <x:v>0.05078125</x:v>
+      </x:c>
+      <x:c r="T7" s="66" t="n">
+        <x:v>0.17</x:v>
+      </x:c>
+      <x:c r="U7" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V7" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="62" t="n">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="B8" s="30" t="str">
+        <x:v>Digital Partner</x:v>
+      </x:c>
+      <x:c r="C8" s="64" t="n">
+        <x:v>4228</x:v>
+      </x:c>
+      <x:c r="D8" s="64" t="n">
+        <x:v>3499</x:v>
+      </x:c>
+      <x:c r="E8" s="64" t="n">
+        <x:v>642</x:v>
+      </x:c>
+      <x:c r="F8" s="66" t="n">
+        <x:v>0.15184484389782402</x:v>
+      </x:c>
+      <x:c r="G8" s="66"/>
+      <x:c r="H8" s="64" t="n">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="I8" s="66" t="n">
+        <x:v>0.470404984423676</x:v>
+      </x:c>
+      <x:c r="J8" s="64" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="K8" s="66" t="n">
+        <x:v>0.09968847352024922</x:v>
+      </x:c>
+      <x:c r="L8" s="64" t="n">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="M8" s="66" t="n">
+        <x:v>0.42990654205607476</x:v>
+      </x:c>
+      <x:c r="N8" s="64" t="n">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="O8" s="66" t="n">
+        <x:v>0.660436137071651</x:v>
+      </x:c>
+      <x:c r="P8" s="64" t="n">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="Q8" s="66" t="n">
+        <x:v>0.2897196261682243</x:v>
+      </x:c>
+      <x:c r="R8" s="64" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="S8" s="66" t="n">
+        <x:v>0.04984423676012461</x:v>
+      </x:c>
+      <x:c r="T8" s="66" t="n">
+        <x:v>0.17</x:v>
+      </x:c>
+      <x:c r="U8" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V8" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="62" t="n">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="B9" s="30" t="str">
+        <x:v>Inbound</x:v>
+      </x:c>
+      <x:c r="C9" s="64" t="n">
+        <x:v>5134</x:v>
+      </x:c>
+      <x:c r="D9" s="64" t="n">
+        <x:v>4291</x:v>
+      </x:c>
+      <x:c r="E9" s="64" t="n">
+        <x:v>764</x:v>
+      </x:c>
+      <x:c r="F9" s="66" t="n">
+        <x:v>0.14881184261784183</x:v>
+      </x:c>
+      <x:c r="G9" s="66"/>
+      <x:c r="H9" s="64" t="n">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="I9" s="66" t="n">
+        <x:v>0.4698952879581152</x:v>
+      </x:c>
+      <x:c r="J9" s="64" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="K9" s="66" t="n">
+        <x:v>0.09947643979057591</x:v>
+      </x:c>
+      <x:c r="L9" s="64" t="n">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="M9" s="66" t="n">
+        <x:v>0.4306282722513089</x:v>
+      </x:c>
+      <x:c r="N9" s="64" t="n">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="O9" s="66" t="n">
+        <x:v>0.6701570680628273</x:v>
+      </x:c>
+      <x:c r="P9" s="64" t="n">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="Q9" s="66" t="n">
+        <x:v>0.2801047120418848</x:v>
+      </x:c>
+      <x:c r="R9" s="64" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="S9" s="66" t="n">
+        <x:v>0.049738219895287955</x:v>
+      </x:c>
+      <x:c r="T9" s="66" t="n">
+        <x:v>0.18000000000000002</x:v>
+      </x:c>
+      <x:c r="U9" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V9" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="62" t="n">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="B10" s="30" t="str">
+        <x:v>Indirect</x:v>
+      </x:c>
+      <x:c r="C10" s="64" t="n">
+        <x:v>3624</x:v>
+      </x:c>
+      <x:c r="D10" s="64" t="n">
+        <x:v>2969</x:v>
+      </x:c>
+      <x:c r="E10" s="64" t="n">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="F10" s="66" t="n">
+        <x:v>0.1534216335540839</x:v>
+      </x:c>
+      <x:c r="G10" s="66"/>
+      <x:c r="H10" s="64" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="I10" s="66" t="n">
+        <x:v>0.460431654676259</x:v>
+      </x:c>
+      <x:c r="J10" s="64" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K10" s="66" t="n">
+        <x:v>0.10971223021582734</x:v>
+      </x:c>
+      <x:c r="L10" s="64" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="M10" s="66" t="n">
+        <x:v>0.42985611510791366</x:v>
+      </x:c>
+      <x:c r="N10" s="64" t="n">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="O10" s="66" t="n">
+        <x:v>0.6600719424460432</x:v>
+      </x:c>
+      <x:c r="P10" s="64" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="Q10" s="66" t="n">
+        <x:v>0.289568345323741</x:v>
+      </x:c>
+      <x:c r="R10" s="64" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="S10" s="66" t="n">
+        <x:v>0.050359712230215826</x:v>
+      </x:c>
+      <x:c r="T10" s="66" t="n">
+        <x:v>0.17</x:v>
+      </x:c>
+      <x:c r="U10" s="66" t="n">
+        <x:v>0.09999999999999999</x:v>
+      </x:c>
+      <x:c r="V10" s="66" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="62" t="n">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="B11" s="30" t="str">
+        <x:v>OBTM</x:v>
+      </x:c>
+      <x:c r="C11" s="64" t="n">
+        <x:v>3322</x:v>
+      </x:c>
+      <x:c r="D11" s="64" t="n">
+        <x:v>2749</x:v>
+      </x:c>
+      <x:c r="E11" s="64" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="F11" s="66" t="n">
+        <x:v>0.15051173991571343</x:v>
+      </x:c>
+      <x:c r="G11" s="66"/>
+      <x:c r="H11" s="64" t="n">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="I11" s="66" t="n">
+        <x:v>0.47</x:v>
+      </x:c>
+      <x:c r="J11" s="64" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="K11" s="66" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L11" s="64" t="n">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="M11" s="66" t="n">
+        <x:v>0.43</x:v>
+      </x:c>
+      <x:c r="N11" s="64" t="n">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="O11" s="66" t="n">
+        <x:v>0.66</x:v>
+      </x:c>
+      <x:c r="P11" s="64" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="Q11" s="66" t="n">
+        <x:v>0.29</x:v>
+      </x:c>
+      <x:c r="R11" s="64" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="S11" s="66" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="T11" s="66" t="n">
+        <x:v>0.17</x:v>
+      </x:c>
+      <x:c r="U11" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V11" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="62" t="n">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="B12" s="30" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="C12" s="64" t="n">
+        <x:v>2416</x:v>
+      </x:c>
+      <x:c r="D12" s="64" t="n">
+        <x:v>1959</x:v>
+      </x:c>
+      <x:c r="E12" s="64" t="n">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="F12" s="66" t="n">
+        <x:v>0.1519039735099338</x:v>
+      </x:c>
+      <x:c r="G12" s="66"/>
+      <x:c r="H12" s="64" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="I12" s="66" t="n">
+        <x:v>0.47956403269754766</x:v>
+      </x:c>
+      <x:c r="J12" s="64" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K12" s="66" t="n">
+        <x:v>0.08991825613079019</x:v>
+      </x:c>
+      <x:c r="L12" s="64" t="n">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="M12" s="66" t="n">
+        <x:v>0.4305177111716621</x:v>
+      </x:c>
+      <x:c r="N12" s="64" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="O12" s="66" t="n">
+        <x:v>0.6512261580381471</x:v>
+      </x:c>
+      <x:c r="P12" s="64" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="Q12" s="66" t="n">
+        <x:v>0.2997275204359673</x:v>
+      </x:c>
+      <x:c r="R12" s="64" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="S12" s="66" t="n">
+        <x:v>0.04904632152588556</x:v>
+      </x:c>
+      <x:c r="T12" s="66" t="n">
+        <x:v>0.17</x:v>
+      </x:c>
+      <x:c r="U12" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V12" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="62" t="n">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="B13" s="30" t="str">
+        <x:v>D2D</x:v>
+      </x:c>
+      <x:c r="C13" s="64" t="n">
+        <x:v>6200</x:v>
+      </x:c>
+      <x:c r="D13" s="64" t="n">
+        <x:v>5045</x:v>
+      </x:c>
+      <x:c r="E13" s="64" t="n">
+        <x:v>964</x:v>
+      </x:c>
+      <x:c r="F13" s="66" t="n">
+        <x:v>0.15548387096774194</x:v>
+      </x:c>
+      <x:c r="G13" s="66" t="n">
+        <x:v>0.029914529914529808</x:v>
+      </x:c>
+      <x:c r="H13" s="64" t="n">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="I13" s="66" t="n">
+        <x:v>0.4699170124481328</x:v>
+      </x:c>
+      <x:c r="J13" s="64" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="K13" s="66" t="n">
+        <x:v>0.0995850622406639</x:v>
+      </x:c>
+      <x:c r="L13" s="64" t="n">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="M13" s="66" t="n">
+        <x:v>0.43049792531120334</x:v>
+      </x:c>
+      <x:c r="N13" s="64" t="n">
+        <x:v>656</x:v>
+      </x:c>
+      <x:c r="O13" s="66" t="n">
+        <x:v>0.6804979253112033</x:v>
+      </x:c>
+      <x:c r="P13" s="64" t="n">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="Q13" s="66" t="n">
+        <x:v>0.2697095435684647</x:v>
+      </x:c>
+      <x:c r="R13" s="64" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="S13" s="66" t="n">
+        <x:v>0.04979253112033195</x:v>
+      </x:c>
+      <x:c r="T13" s="66" t="n">
+        <x:v>0.18400000000000002</x:v>
+      </x:c>
+      <x:c r="U13" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V13" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="62" t="n">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="B14" s="30" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="C14" s="64" t="n">
+        <x:v>5580</x:v>
+      </x:c>
+      <x:c r="D14" s="64" t="n">
+        <x:v>4773</x:v>
+      </x:c>
+      <x:c r="E14" s="64" t="n">
+        <x:v>791</x:v>
+      </x:c>
+      <x:c r="F14" s="66" t="n">
+        <x:v>0.14175627240143368</x:v>
+      </x:c>
+      <x:c r="G14" s="66" t="n">
+        <x:v>0.02994791666666674</x:v>
+      </x:c>
+      <x:c r="H14" s="64" t="n">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="I14" s="66" t="n">
+        <x:v>0.49051833122629585</x:v>
+      </x:c>
+      <x:c r="J14" s="64" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="K14" s="66" t="n">
+        <x:v>0.09987357774968394</x:v>
+      </x:c>
+      <x:c r="L14" s="64" t="n">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="M14" s="66" t="n">
+        <x:v>0.40960809102402024</x:v>
+      </x:c>
+      <x:c r="N14" s="64" t="n">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="O14" s="66" t="n">
+        <x:v>0.6599241466498104</x:v>
+      </x:c>
+      <x:c r="P14" s="64" t="n">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="Q14" s="66" t="n">
+        <x:v>0.2895069532237674</x:v>
+      </x:c>
+      <x:c r="R14" s="64" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="S14" s="66" t="n">
+        <x:v>0.05056890012642225</x:v>
+      </x:c>
+      <x:c r="T14" s="66" t="n">
+        <x:v>0.17400000000000002</x:v>
+      </x:c>
+      <x:c r="U14" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V14" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="62" t="n">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="B15" s="30" t="str">
+        <x:v>Digital Partner</x:v>
+      </x:c>
+      <x:c r="C15" s="64" t="n">
+        <x:v>4340</x:v>
+      </x:c>
+      <x:c r="D15" s="64" t="n">
+        <x:v>3604</x:v>
+      </x:c>
+      <x:c r="E15" s="64" t="n">
+        <x:v>661</x:v>
+      </x:c>
+      <x:c r="F15" s="66" t="n">
+        <x:v>0.1523041474654378</x:v>
+      </x:c>
+      <x:c r="G15" s="66" t="n">
+        <x:v>0.029595015576324046</x:v>
+      </x:c>
+      <x:c r="H15" s="64" t="n">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="I15" s="66" t="n">
+        <x:v>0.4795763993948563</x:v>
+      </x:c>
+      <x:c r="J15" s="64" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="K15" s="66" t="n">
+        <x:v>0.09984871406959153</x:v>
+      </x:c>
+      <x:c r="L15" s="64" t="n">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="M15" s="66" t="n">
+        <x:v>0.4205748865355522</x:v>
+      </x:c>
+      <x:c r="N15" s="64" t="n">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="O15" s="66" t="n">
+        <x:v>0.670196671709531</x:v>
+      </x:c>
+      <x:c r="P15" s="64" t="n">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="Q15" s="66" t="n">
+        <x:v>0.27987897125567324</x:v>
+      </x:c>
+      <x:c r="R15" s="64" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S15" s="66" t="n">
+        <x:v>0.049924357034795766</x:v>
+      </x:c>
+      <x:c r="T15" s="66" t="n">
+        <x:v>0.17400000000000002</x:v>
+      </x:c>
+      <x:c r="U15" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V15" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="62" t="n">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="B16" s="30" t="str">
+        <x:v>Inbound</x:v>
+      </x:c>
+      <x:c r="C16" s="64" t="n">
+        <x:v>5270</x:v>
+      </x:c>
+      <x:c r="D16" s="64" t="n">
+        <x:v>4420</x:v>
+      </x:c>
+      <x:c r="E16" s="64" t="n">
+        <x:v>787</x:v>
+      </x:c>
+      <x:c r="F16" s="66" t="n">
+        <x:v>0.1493358633776091</x:v>
+      </x:c>
+      <x:c r="G16" s="66" t="n">
+        <x:v>0.030104712041884918</x:v>
+      </x:c>
+      <x:c r="H16" s="64" t="n">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="I16" s="66" t="n">
+        <x:v>0.48030495552731894</x:v>
+      </x:c>
+      <x:c r="J16" s="64" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="K16" s="66" t="n">
+        <x:v>0.10038119440914867</x:v>
+      </x:c>
+      <x:c r="L16" s="64" t="n">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="M16" s="66" t="n">
+        <x:v>0.4193138500635324</x:v>
+      </x:c>
+      <x:c r="N16" s="64" t="n">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="O16" s="66" t="n">
+        <x:v>0.6797966963151207</x:v>
+      </x:c>
+      <x:c r="P16" s="64" t="n">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="Q16" s="66" t="n">
+        <x:v>0.26937738246505716</x:v>
+      </x:c>
+      <x:c r="R16" s="64" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="S16" s="66" t="n">
+        <x:v>0.05082592121982211</x:v>
+      </x:c>
+      <x:c r="T16" s="66" t="n">
+        <x:v>0.18400000000000002</x:v>
+      </x:c>
+      <x:c r="U16" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V16" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="62" t="n">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="B17" s="30" t="str">
+        <x:v>Indirect</x:v>
+      </x:c>
+      <x:c r="C17" s="64" t="n">
+        <x:v>3720</x:v>
+      </x:c>
+      <x:c r="D17" s="64" t="n">
+        <x:v>3058</x:v>
+      </x:c>
+      <x:c r="E17" s="64" t="n">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="F17" s="66" t="n">
+        <x:v>0.15403225806451612</x:v>
+      </x:c>
+      <x:c r="G17" s="66" t="n">
+        <x:v>0.030575539568345356</x:v>
+      </x:c>
+      <x:c r="H17" s="64" t="n">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="I17" s="66" t="n">
+        <x:v>0.4694589877835951</x:v>
+      </x:c>
+      <x:c r="J17" s="64" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="K17" s="66" t="n">
+        <x:v>0.1099476439790576</x:v>
+      </x:c>
+      <x:c r="L17" s="64" t="n">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="M17" s="66" t="n">
+        <x:v>0.4205933682373473</x:v>
+      </x:c>
+      <x:c r="N17" s="64" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="O17" s="66" t="n">
+        <x:v>0.6701570680628273</x:v>
+      </x:c>
+      <x:c r="P17" s="64" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="Q17" s="66" t="n">
+        <x:v>0.2792321116928447</x:v>
+      </x:c>
+      <x:c r="R17" s="64" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="S17" s="66" t="n">
+        <x:v>0.0506108202443281</x:v>
+      </x:c>
+      <x:c r="T17" s="66" t="n">
+        <x:v>0.17400000000000002</x:v>
+      </x:c>
+      <x:c r="U17" s="66" t="n">
+        <x:v>0.09999999999999999</x:v>
+      </x:c>
+      <x:c r="V17" s="66" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="62" t="n">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="B18" s="30" t="str">
+        <x:v>OBTM</x:v>
+      </x:c>
+      <x:c r="C18" s="64" t="n">
+        <x:v>3410</x:v>
+      </x:c>
+      <x:c r="D18" s="64" t="n">
+        <x:v>2832</x:v>
+      </x:c>
+      <x:c r="E18" s="64" t="n">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="F18" s="66" t="n">
+        <x:v>0.15102639296187684</x:v>
+      </x:c>
+      <x:c r="G18" s="66" t="n">
+        <x:v>0.030000000000000027</x:v>
+      </x:c>
+      <x:c r="H18" s="64" t="n">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="I18" s="66" t="n">
+        <x:v>0.4796116504854369</x:v>
+      </x:c>
+      <x:c r="J18" s="64" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="K18" s="66" t="n">
+        <x:v>0.10097087378640776</x:v>
+      </x:c>
+      <x:c r="L18" s="64" t="n">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="M18" s="66" t="n">
+        <x:v>0.41941747572815535</x:v>
+      </x:c>
+      <x:c r="N18" s="64" t="n">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="O18" s="66" t="n">
+        <x:v>0.6699029126213593</x:v>
+      </x:c>
+      <x:c r="P18" s="64" t="n">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="Q18" s="66" t="n">
+        <x:v>0.2796116504854369</x:v>
+      </x:c>
+      <x:c r="R18" s="64" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="S18" s="66" t="n">
+        <x:v>0.05048543689320388</x:v>
+      </x:c>
+      <x:c r="T18" s="66" t="n">
+        <x:v>0.17400000000000002</x:v>
+      </x:c>
+      <x:c r="U18" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V18" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="62" t="n">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="B19" s="30" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="C19" s="64" t="n">
+        <x:v>2480</x:v>
+      </x:c>
+      <x:c r="D19" s="64" t="n">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="E19" s="64" t="n">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="F19" s="66" t="n">
+        <x:v>0.15241935483870966</x:v>
+      </x:c>
+      <x:c r="G19" s="66" t="n">
+        <x:v>0.02997275204359684</x:v>
+      </x:c>
+      <x:c r="H19" s="64" t="n">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="I19" s="66" t="n">
+        <x:v>0.4894179894179894</x:v>
+      </x:c>
+      <x:c r="J19" s="64" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K19" s="66" t="n">
+        <x:v>0.08994708994708994</x:v>
+      </x:c>
+      <x:c r="L19" s="64" t="n">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="M19" s="66" t="n">
+        <x:v>0.42063492063492064</x:v>
+      </x:c>
+      <x:c r="N19" s="64" t="n">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="O19" s="66" t="n">
+        <x:v>0.6587301587301587</x:v>
+      </x:c>
+      <x:c r="P19" s="64" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="Q19" s="66" t="n">
+        <x:v>0.291005291005291</x:v>
+      </x:c>
+      <x:c r="R19" s="64" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="S19" s="66" t="n">
+        <x:v>0.05026455026455026</x:v>
+      </x:c>
+      <x:c r="T19" s="66" t="n">
+        <x:v>0.17400000000000002</x:v>
+      </x:c>
+      <x:c r="U19" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V19" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="62" t="n">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="B20" s="30" t="str">
+        <x:v>D2D</x:v>
+      </x:c>
+      <x:c r="C20" s="64" t="n">
+        <x:v>6380</x:v>
+      </x:c>
+      <x:c r="D20" s="64" t="n">
+        <x:v>5192</x:v>
+      </x:c>
+      <x:c r="E20" s="64" t="n">
+        <x:v>993</x:v>
+      </x:c>
+      <x:c r="F20" s="66" t="n">
+        <x:v>0.15564263322884012</x:v>
+      </x:c>
+      <x:c r="G20" s="66" t="n">
+        <x:v>0.030082987551867113</x:v>
+      </x:c>
+      <x:c r="H20" s="64" t="n">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="I20" s="66" t="n">
+        <x:v>0.4602215508559919</x:v>
+      </x:c>
+      <x:c r="J20" s="64" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="K20" s="66" t="n">
+        <x:v>0.09969788519637462</x:v>
+      </x:c>
+      <x:c r="L20" s="64" t="n">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="M20" s="66" t="n">
+        <x:v>0.44008056394763345</x:v>
+      </x:c>
+      <x:c r="N20" s="64" t="n">
+        <x:v>665</x:v>
+      </x:c>
+      <x:c r="O20" s="66" t="n">
+        <x:v>0.6696878147029205</x:v>
+      </x:c>
+      <x:c r="P20" s="64" t="n">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="Q20" s="66" t="n">
+        <x:v>0.2799597180261833</x:v>
+      </x:c>
+      <x:c r="R20" s="64" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="S20" s="66" t="n">
+        <x:v>0.050352467270896276</x:v>
+      </x:c>
+      <x:c r="T20" s="66" t="n">
+        <x:v>0.18800000000000003</x:v>
+      </x:c>
+      <x:c r="U20" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V20" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="62" t="n">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="B21" s="30" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="C21" s="64" t="n">
+        <x:v>5742</x:v>
+      </x:c>
+      <x:c r="D21" s="64" t="n">
+        <x:v>4912</x:v>
+      </x:c>
+      <x:c r="E21" s="64" t="n">
+        <x:v>815</x:v>
+      </x:c>
+      <x:c r="F21" s="66" t="n">
+        <x:v>0.14193660745384884</x:v>
+      </x:c>
+      <x:c r="G21" s="66" t="n">
+        <x:v>0.03034134007585343</x:v>
+      </x:c>
+      <x:c r="H21" s="64" t="n">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="I21" s="66" t="n">
+        <x:v>0.47975460122699387</x:v>
+      </x:c>
+      <x:c r="J21" s="64" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="K21" s="66" t="n">
+        <x:v>0.10061349693251534</x:v>
+      </x:c>
+      <x:c r="L21" s="64" t="n">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="M21" s="66" t="n">
+        <x:v>0.4196319018404908</x:v>
+      </x:c>
+      <x:c r="N21" s="64" t="n">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="O21" s="66" t="n">
+        <x:v>0.6503067484662577</x:v>
+      </x:c>
+      <x:c r="P21" s="64" t="n">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="Q21" s="66" t="n">
+        <x:v>0.29938650306748466</x:v>
+      </x:c>
+      <x:c r="R21" s="64" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="S21" s="66" t="n">
+        <x:v>0.05030674846625767</x:v>
+      </x:c>
+      <x:c r="T21" s="66" t="n">
+        <x:v>0.17800000000000002</x:v>
+      </x:c>
+      <x:c r="U21" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V21" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="62" t="n">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="B22" s="30" t="str">
+        <x:v>Digital Partner</x:v>
+      </x:c>
+      <x:c r="C22" s="64" t="n">
+        <x:v>4466</x:v>
+      </x:c>
+      <x:c r="D22" s="64" t="n">
+        <x:v>3709</x:v>
+      </x:c>
+      <x:c r="E22" s="64" t="n">
+        <x:v>681</x:v>
+      </x:c>
+      <x:c r="F22" s="66" t="n">
+        <x:v>0.15248544558889388</x:v>
+      </x:c>
+      <x:c r="G22" s="66" t="n">
+        <x:v>0.030257186081694476</x:v>
+      </x:c>
+      <x:c r="H22" s="64" t="n">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="I22" s="66" t="n">
+        <x:v>0.4698972099853157</x:v>
+      </x:c>
+      <x:c r="J22" s="64" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="K22" s="66" t="n">
+        <x:v>0.09985315712187959</x:v>
+      </x:c>
+      <x:c r="L22" s="64" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M22" s="66" t="n">
+        <x:v>0.4302496328928047</x:v>
+      </x:c>
+      <x:c r="N22" s="64" t="n">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="O22" s="66" t="n">
+        <x:v>0.6593245227606461</x:v>
+      </x:c>
+      <x:c r="P22" s="64" t="n">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="Q22" s="66" t="n">
+        <x:v>0.28928046989721</x:v>
+      </x:c>
+      <x:c r="R22" s="64" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="S22" s="66" t="n">
+        <x:v>0.0513950073421439</x:v>
+      </x:c>
+      <x:c r="T22" s="66" t="n">
+        <x:v>0.17800000000000002</x:v>
+      </x:c>
+      <x:c r="U22" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V22" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="62" t="n">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="B23" s="30" t="str">
+        <x:v>Inbound</x:v>
+      </x:c>
+      <x:c r="C23" s="64" t="n">
+        <x:v>5423</x:v>
+      </x:c>
+      <x:c r="D23" s="64" t="n">
+        <x:v>4549</x:v>
+      </x:c>
+      <x:c r="E23" s="64" t="n">
+        <x:v>811</x:v>
+      </x:c>
+      <x:c r="F23" s="66" t="n">
+        <x:v>0.14954822054213535</x:v>
+      </x:c>
+      <x:c r="G23" s="66" t="n">
+        <x:v>0.030495552731893305</x:v>
+      </x:c>
+      <x:c r="H23" s="64" t="n">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="I23" s="66" t="n">
+        <x:v>0.46979038224414305</x:v>
+      </x:c>
+      <x:c r="J23" s="64" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="K23" s="66" t="n">
+        <x:v>0.0998766954377312</x:v>
+      </x:c>
+      <x:c r="L23" s="64" t="n">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="M23" s="66" t="n">
+        <x:v>0.43033292231812575</x:v>
+      </x:c>
+      <x:c r="N23" s="64" t="n">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="O23" s="66" t="n">
+        <x:v>0.6695437731196054</x:v>
+      </x:c>
+      <x:c r="P23" s="64" t="n">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="Q23" s="66" t="n">
+        <x:v>0.279901356350185</x:v>
+      </x:c>
+      <x:c r="R23" s="64" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="S23" s="66" t="n">
+        <x:v>0.05055487053020962</x:v>
+      </x:c>
+      <x:c r="T23" s="66" t="n">
+        <x:v>0.18800000000000003</x:v>
+      </x:c>
+      <x:c r="U23" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V23" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="62" t="n">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="B24" s="30" t="str">
+        <x:v>Indirect</x:v>
+      </x:c>
+      <x:c r="C24" s="64" t="n">
+        <x:v>3828</x:v>
+      </x:c>
+      <x:c r="D24" s="64" t="n">
+        <x:v>3147</x:v>
+      </x:c>
+      <x:c r="E24" s="64" t="n">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="F24" s="66" t="n">
+        <x:v>0.15412748171368862</x:v>
+      </x:c>
+      <x:c r="G24" s="66" t="n">
+        <x:v>0.029668411867364686</x:v>
+      </x:c>
+      <x:c r="H24" s="64" t="n">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="I24" s="66" t="n">
+        <x:v>0.45932203389830506</x:v>
+      </x:c>
+      <x:c r="J24" s="64" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="K24" s="66" t="n">
+        <x:v>0.11016949152542373</x:v>
+      </x:c>
+      <x:c r="L24" s="64" t="n">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="M24" s="66" t="n">
+        <x:v>0.43050847457627117</x:v>
+      </x:c>
+      <x:c r="N24" s="64" t="n">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="O24" s="66" t="n">
+        <x:v>0.6593220338983051</x:v>
+      </x:c>
+      <x:c r="P24" s="64" t="n">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="Q24" s="66" t="n">
+        <x:v>0.28983050847457625</x:v>
+      </x:c>
+      <x:c r="R24" s="64" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="S24" s="66" t="n">
+        <x:v>0.05084745762711865</x:v>
+      </x:c>
+      <x:c r="T24" s="66" t="n">
+        <x:v>0.17800000000000002</x:v>
+      </x:c>
+      <x:c r="U24" s="66" t="n">
+        <x:v>0.09999999999999999</x:v>
+      </x:c>
+      <x:c r="V24" s="66" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="62" t="n">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="B25" s="30" t="str">
+        <x:v>OBTM</x:v>
+      </x:c>
+      <x:c r="C25" s="64" t="n">
+        <x:v>3509</x:v>
+      </x:c>
+      <x:c r="D25" s="64" t="n">
+        <x:v>2914</x:v>
+      </x:c>
+      <x:c r="E25" s="64" t="n">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="F25" s="66" t="n">
+        <x:v>0.15104018238814476</x:v>
+      </x:c>
+      <x:c r="G25" s="66" t="n">
+        <x:v>0.029126213592232997</x:v>
+      </x:c>
+      <x:c r="H25" s="64" t="n">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="I25" s="66" t="n">
+        <x:v>0.469811320754717</x:v>
+      </x:c>
+      <x:c r="J25" s="64" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K25" s="66" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L25" s="64" t="n">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="M25" s="66" t="n">
+        <x:v>0.43018867924528303</x:v>
+      </x:c>
+      <x:c r="N25" s="64" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="O25" s="66" t="n">
+        <x:v>0.660377358490566</x:v>
+      </x:c>
+      <x:c r="P25" s="64" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="Q25" s="66" t="n">
+        <x:v>0.29056603773584905</x:v>
+      </x:c>
+      <x:c r="R25" s="64" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="S25" s="66" t="n">
+        <x:v>0.04905660377358491</x:v>
+      </x:c>
+      <x:c r="T25" s="66" t="n">
+        <x:v>0.17800000000000002</x:v>
+      </x:c>
+      <x:c r="U25" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V25" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="62" t="n">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="B26" s="30" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="C26" s="64" t="n">
+        <x:v>2552</x:v>
+      </x:c>
+      <x:c r="D26" s="64" t="n">
+        <x:v>2077</x:v>
+      </x:c>
+      <x:c r="E26" s="64" t="n">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="F26" s="66" t="n">
+        <x:v>0.1524294670846395</x:v>
+      </x:c>
+      <x:c r="G26" s="66" t="n">
+        <x:v>0.02910052910052907</x:v>
+      </x:c>
+      <x:c r="H26" s="64" t="n">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="I26" s="66" t="n">
+        <x:v>0.480719794344473</x:v>
+      </x:c>
+      <x:c r="J26" s="64" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="K26" s="66" t="n">
+        <x:v>0.08997429305912596</x:v>
+      </x:c>
+      <x:c r="L26" s="64" t="n">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="M26" s="66" t="n">
+        <x:v>0.42930591259640105</x:v>
+      </x:c>
+      <x:c r="N26" s="64" t="n">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="O26" s="66" t="n">
+        <x:v>0.6503856041131105</x:v>
+      </x:c>
+      <x:c r="P26" s="64" t="n">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="Q26" s="66" t="n">
+        <x:v>0.30077120822622105</x:v>
+      </x:c>
+      <x:c r="R26" s="64" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="S26" s="66" t="n">
+        <x:v>0.04884318766066838</x:v>
+      </x:c>
+      <x:c r="T26" s="66" t="n">
+        <x:v>0.17800000000000002</x:v>
+      </x:c>
+      <x:c r="U26" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V26" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="62" t="n">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="B27" s="30" t="str">
+        <x:v>D2D</x:v>
+      </x:c>
+      <x:c r="C27" s="64" t="n">
+        <x:v>6560</x:v>
+      </x:c>
+      <x:c r="D27" s="64" t="n">
+        <x:v>5330</x:v>
+      </x:c>
+      <x:c r="E27" s="64" t="n">
+        <x:v>1022</x:v>
+      </x:c>
+      <x:c r="F27" s="66" t="n">
+        <x:v>0.15579268292682927</x:v>
+      </x:c>
+      <x:c r="G27" s="66" t="n">
+        <x:v>0.02920443101711978</x:v>
+      </x:c>
+      <x:c r="H27" s="64" t="n">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="I27" s="66" t="n">
+        <x:v>0.4500978473581213</x:v>
+      </x:c>
+      <x:c r="J27" s="64" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="K27" s="66" t="n">
+        <x:v>0.1095890410958904</x:v>
+      </x:c>
+      <x:c r="L27" s="64" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="M27" s="66" t="n">
+        <x:v>0.44031311154598823</x:v>
+      </x:c>
+      <x:c r="N27" s="64" t="n">
+        <x:v>695</x:v>
+      </x:c>
+      <x:c r="O27" s="66" t="n">
+        <x:v>0.6800391389432485</x:v>
+      </x:c>
+      <x:c r="P27" s="64" t="n">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="Q27" s="66" t="n">
+        <x:v>0.2700587084148728</x:v>
+      </x:c>
+      <x:c r="R27" s="64" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="S27" s="66" t="n">
+        <x:v>0.049902152641878667</x:v>
+      </x:c>
+      <x:c r="T27" s="66" t="n">
+        <x:v>0.19200000000000003</x:v>
+      </x:c>
+      <x:c r="U27" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V27" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="62" t="n">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="B28" s="30" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="C28" s="64" t="n">
+        <x:v>5904</x:v>
+      </x:c>
+      <x:c r="D28" s="64" t="n">
+        <x:v>5041</x:v>
+      </x:c>
+      <x:c r="E28" s="64" t="n">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="F28" s="66" t="n">
+        <x:v>0.14227642276422764</x:v>
+      </x:c>
+      <x:c r="G28" s="66" t="n">
+        <x:v>0.030674846625766916</x:v>
+      </x:c>
+      <x:c r="H28" s="64" t="n">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="I28" s="66" t="n">
+        <x:v>0.47023809523809523</x:v>
+      </x:c>
+      <x:c r="J28" s="64" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K28" s="66" t="n">
+        <x:v>0.10952380952380952</x:v>
+      </x:c>
+      <x:c r="L28" s="64" t="n">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="M28" s="66" t="n">
+        <x:v>0.42023809523809524</x:v>
+      </x:c>
+      <x:c r="N28" s="64" t="n">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="O28" s="66" t="n">
+        <x:v>0.6595238095238095</x:v>
+      </x:c>
+      <x:c r="P28" s="64" t="n">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="Q28" s="66" t="n">
+        <x:v>0.2904761904761905</x:v>
+      </x:c>
+      <x:c r="R28" s="64" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="S28" s="66" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="T28" s="66" t="n">
+        <x:v>0.18200000000000002</x:v>
+      </x:c>
+      <x:c r="U28" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V28" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="62" t="n">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="B29" s="30" t="str">
+        <x:v>Digital Partner</x:v>
+      </x:c>
+      <x:c r="C29" s="64" t="n">
+        <x:v>4592</x:v>
+      </x:c>
+      <x:c r="D29" s="64" t="n">
+        <x:v>3807</x:v>
+      </x:c>
+      <x:c r="E29" s="64" t="n">
+        <x:v>702</x:v>
+      </x:c>
+      <x:c r="F29" s="66" t="n">
+        <x:v>0.1528745644599303</x:v>
+      </x:c>
+      <x:c r="G29" s="66" t="n">
+        <x:v>0.03083700440528636</x:v>
+      </x:c>
+      <x:c r="H29" s="64" t="n">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="I29" s="66" t="n">
+        <x:v>0.4601139601139601</x:v>
+      </x:c>
+      <x:c r="J29" s="64" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="K29" s="66" t="n">
+        <x:v>0.10968660968660969</x:v>
+      </x:c>
+      <x:c r="L29" s="64" t="n">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="M29" s="66" t="n">
+        <x:v>0.4301994301994302</x:v>
+      </x:c>
+      <x:c r="N29" s="64" t="n">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="O29" s="66" t="n">
+        <x:v>0.6695156695156695</x:v>
+      </x:c>
+      <x:c r="P29" s="64" t="n">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="Q29" s="66" t="n">
+        <x:v>0.28062678062678065</x:v>
+      </x:c>
+      <x:c r="R29" s="64" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="S29" s="66" t="n">
+        <x:v>0.04985754985754986</x:v>
+      </x:c>
+      <x:c r="T29" s="66" t="n">
+        <x:v>0.18200000000000002</x:v>
+      </x:c>
+      <x:c r="U29" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V29" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="62" t="n">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="B30" s="30" t="str">
+        <x:v>Inbound</x:v>
+      </x:c>
+      <x:c r="C30" s="64" t="n">
+        <x:v>5576</x:v>
+      </x:c>
+      <x:c r="D30" s="64" t="n">
+        <x:v>4669</x:v>
+      </x:c>
+      <x:c r="E30" s="64" t="n">
+        <x:v>835</x:v>
+      </x:c>
+      <x:c r="F30" s="66" t="n">
+        <x:v>0.14974892395982783</x:v>
+      </x:c>
+      <x:c r="G30" s="66" t="n">
+        <x:v>0.0295930949445129</x:v>
+      </x:c>
+      <x:c r="H30" s="64" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="I30" s="66" t="n">
+        <x:v>0.4598802395209581</x:v>
+      </x:c>
+      <x:c r="J30" s="64" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K30" s="66" t="n">
+        <x:v>0.11017964071856287</x:v>
+      </x:c>
+      <x:c r="L30" s="64" t="n">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="M30" s="66" t="n">
+        <x:v>0.429940119760479</x:v>
+      </x:c>
+      <x:c r="N30" s="64" t="n">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="O30" s="66" t="n">
+        <x:v>0.6802395209580838</x:v>
+      </x:c>
+      <x:c r="P30" s="64" t="n">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="Q30" s="66" t="n">
+        <x:v>0.2694610778443114</x:v>
+      </x:c>
+      <x:c r="R30" s="64" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="S30" s="66" t="n">
+        <x:v>0.05029940119760479</x:v>
+      </x:c>
+      <x:c r="T30" s="66" t="n">
+        <x:v>0.19200000000000003</x:v>
+      </x:c>
+      <x:c r="U30" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V30" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="62" t="n">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="B31" s="30" t="str">
+        <x:v>Indirect</x:v>
+      </x:c>
+      <x:c r="C31" s="64" t="n">
+        <x:v>3936</x:v>
+      </x:c>
+      <x:c r="D31" s="64" t="n">
+        <x:v>3230</x:v>
+      </x:c>
+      <x:c r="E31" s="64" t="n">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="F31" s="66" t="n">
+        <x:v>0.15421747967479674</x:v>
+      </x:c>
+      <x:c r="G31" s="66" t="n">
+        <x:v>0.028813559322034</x:v>
+      </x:c>
+      <x:c r="H31" s="64" t="n">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="I31" s="66" t="n">
+        <x:v>0.4497528830313015</x:v>
+      </x:c>
+      <x:c r="J31" s="64" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="K31" s="66" t="n">
+        <x:v>0.12026359143327842</x:v>
+      </x:c>
+      <x:c r="L31" s="64" t="n">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="M31" s="66" t="n">
+        <x:v>0.4299835255354201</x:v>
+      </x:c>
+      <x:c r="N31" s="64" t="n">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="O31" s="66" t="n">
+        <x:v>0.6705107084019769</x:v>
+      </x:c>
+      <x:c r="P31" s="64" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="Q31" s="66" t="n">
+        <x:v>0.2800658978583196</x:v>
+      </x:c>
+      <x:c r="R31" s="64" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="S31" s="66" t="n">
+        <x:v>0.04942339373970346</x:v>
+      </x:c>
+      <x:c r="T31" s="66" t="n">
+        <x:v>0.18200000000000002</x:v>
+      </x:c>
+      <x:c r="U31" s="66" t="n">
+        <x:v>0.09999999999999999</x:v>
+      </x:c>
+      <x:c r="V31" s="66" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="62" t="n">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="B32" s="30" t="str">
+        <x:v>OBTM</x:v>
+      </x:c>
+      <x:c r="C32" s="64" t="n">
+        <x:v>3608</x:v>
+      </x:c>
+      <x:c r="D32" s="64" t="n">
+        <x:v>2991</x:v>
+      </x:c>
+      <x:c r="E32" s="64" t="n">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="F32" s="66" t="n">
+        <x:v>0.15133037694013304</x:v>
+      </x:c>
+      <x:c r="G32" s="66" t="n">
+        <x:v>0.030188679245283012</x:v>
+      </x:c>
+      <x:c r="H32" s="64" t="n">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="I32" s="66" t="n">
+        <x:v>0.4597069597069597</x:v>
+      </x:c>
+      <x:c r="J32" s="64" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K32" s="66" t="n">
+        <x:v>0.10989010989010989</x:v>
+      </x:c>
+      <x:c r="L32" s="64" t="n">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="M32" s="66" t="n">
+        <x:v>0.43040293040293043</x:v>
+      </x:c>
+      <x:c r="N32" s="64" t="n">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="O32" s="66" t="n">
+        <x:v>0.6703296703296703</x:v>
+      </x:c>
+      <x:c r="P32" s="64" t="n">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="Q32" s="66" t="n">
+        <x:v>0.2802197802197802</x:v>
+      </x:c>
+      <x:c r="R32" s="64" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="S32" s="66" t="n">
+        <x:v>0.04945054945054945</x:v>
+      </x:c>
+      <x:c r="T32" s="66" t="n">
+        <x:v>0.18200000000000002</x:v>
+      </x:c>
+      <x:c r="U32" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V32" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="62" t="n">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="B33" s="30" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="C33" s="64" t="n">
+        <x:v>2624</x:v>
+      </x:c>
+      <x:c r="D33" s="64" t="n">
+        <x:v>2132</x:v>
+      </x:c>
+      <x:c r="E33" s="64" t="n">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="F33" s="66" t="n">
+        <x:v>0.15282012195121952</x:v>
+      </x:c>
+      <x:c r="G33" s="66" t="n">
+        <x:v>0.03084832904884327</x:v>
+      </x:c>
+      <x:c r="H33" s="64" t="n">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="I33" s="66" t="n">
+        <x:v>0.4688279301745636</x:v>
+      </x:c>
+      <x:c r="J33" s="64" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K33" s="66" t="n">
+        <x:v>0.09975062344139651</x:v>
+      </x:c>
+      <x:c r="L33" s="64" t="n">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="M33" s="66" t="n">
+        <x:v>0.4314214463840399</x:v>
+      </x:c>
+      <x:c r="N33" s="64" t="n">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="O33" s="66" t="n">
+        <x:v>0.6608478802992519</x:v>
+      </x:c>
+      <x:c r="P33" s="64" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="Q33" s="66" t="n">
+        <x:v>0.2892768079800499</x:v>
+      </x:c>
+      <x:c r="R33" s="64" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="S33" s="66" t="n">
+        <x:v>0.04987531172069826</x:v>
+      </x:c>
+      <x:c r="T33" s="66" t="n">
+        <x:v>0.18200000000000002</x:v>
+      </x:c>
+      <x:c r="U33" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V33" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="62" t="n">
+        <x:v>46143</x:v>
+      </x:c>
+      <x:c r="B34" s="30" t="str">
+        <x:v>D2D</x:v>
+      </x:c>
+      <x:c r="C34" s="64" t="n">
+        <x:v>6740</x:v>
+      </x:c>
+      <x:c r="D34" s="64" t="n">
+        <x:v>5486</x:v>
+      </x:c>
+      <x:c r="E34" s="64" t="n">
+        <x:v>1053</x:v>
+      </x:c>
+      <x:c r="F34" s="66" t="n">
+        <x:v>0.15623145400593472</x:v>
+      </x:c>
+      <x:c r="G34" s="66" t="n">
+        <x:v>0.03033268101761255</x:v>
+      </x:c>
+      <x:c r="H34" s="64" t="n">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="I34" s="66" t="n">
+        <x:v>0.45963912630579296</x:v>
+      </x:c>
+      <x:c r="J34" s="64" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="K34" s="66" t="n">
+        <x:v>0.09971509971509972</x:v>
+      </x:c>
+      <x:c r="L34" s="64" t="n">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="M34" s="66" t="n">
+        <x:v>0.4406457739791073</x:v>
+      </x:c>
+      <x:c r="N34" s="64" t="n">
+        <x:v>727</x:v>
+      </x:c>
+      <x:c r="O34" s="66" t="n">
+        <x:v>0.6904083570750238</x:v>
+      </x:c>
+      <x:c r="P34" s="64" t="n">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="Q34" s="66" t="n">
+        <x:v>0.26020892687559355</x:v>
+      </x:c>
+      <x:c r="R34" s="64" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="S34" s="66" t="n">
+        <x:v>0.04938271604938271</x:v>
+      </x:c>
+      <x:c r="T34" s="66" t="n">
+        <x:v>0.196</x:v>
+      </x:c>
+      <x:c r="U34" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V34" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="62" t="n">
+        <x:v>46143</x:v>
+      </x:c>
+      <x:c r="B35" s="30" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="C35" s="64" t="n">
+        <x:v>6066</x:v>
+      </x:c>
+      <x:c r="D35" s="64" t="n">
+        <x:v>5190</x:v>
+      </x:c>
+      <x:c r="E35" s="64" t="n">
+        <x:v>865</x:v>
+      </x:c>
+      <x:c r="F35" s="66" t="n">
+        <x:v>0.14259808770194526</x:v>
+      </x:c>
+      <x:c r="G35" s="66" t="n">
+        <x:v>0.029761904761904656</x:v>
+      </x:c>
+      <x:c r="H35" s="64" t="n">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="I35" s="66" t="n">
+        <x:v>0.4797687861271676</x:v>
+      </x:c>
+      <x:c r="J35" s="64" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="K35" s="66" t="n">
+        <x:v>0.09942196531791908</x:v>
+      </x:c>
+      <x:c r="L35" s="64" t="n">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="M35" s="66" t="n">
+        <x:v>0.4208092485549133</x:v>
+      </x:c>
+      <x:c r="N35" s="64" t="n">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="O35" s="66" t="n">
+        <x:v>0.6705202312138728</x:v>
+      </x:c>
+      <x:c r="P35" s="64" t="n">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="Q35" s="66" t="n">
+        <x:v>0.27976878612716766</x:v>
+      </x:c>
+      <x:c r="R35" s="64" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="S35" s="66" t="n">
+        <x:v>0.04971098265895954</x:v>
+      </x:c>
+      <x:c r="T35" s="66" t="n">
+        <x:v>0.186</x:v>
+      </x:c>
+      <x:c r="U35" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V35" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="62" t="n">
+        <x:v>46143</x:v>
+      </x:c>
+      <x:c r="B36" s="30" t="str">
+        <x:v>Digital Partner</x:v>
+      </x:c>
+      <x:c r="C36" s="64" t="n">
+        <x:v>4718</x:v>
+      </x:c>
+      <x:c r="D36" s="64" t="n">
+        <x:v>3919</x:v>
+      </x:c>
+      <x:c r="E36" s="64" t="n">
+        <x:v>723</x:v>
+      </x:c>
+      <x:c r="F36" s="66" t="n">
+        <x:v>0.1532428995337007</x:v>
+      </x:c>
+      <x:c r="G36" s="66" t="n">
+        <x:v>0.029914529914529808</x:v>
+      </x:c>
+      <x:c r="H36" s="64" t="n">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="I36" s="66" t="n">
+        <x:v>0.4702627939142462</x:v>
+      </x:c>
+      <x:c r="J36" s="64" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="K36" s="66" t="n">
+        <x:v>0.0995850622406639</x:v>
+      </x:c>
+      <x:c r="L36" s="64" t="n">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="M36" s="66" t="n">
+        <x:v>0.43015214384508993</x:v>
+      </x:c>
+      <x:c r="N36" s="64" t="n">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="O36" s="66" t="n">
+        <x:v>0.6804979253112033</x:v>
+      </x:c>
+      <x:c r="P36" s="64" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="Q36" s="66" t="n">
+        <x:v>0.2697095435684647</x:v>
+      </x:c>
+      <x:c r="R36" s="64" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="S36" s="66" t="n">
+        <x:v>0.04979253112033195</x:v>
+      </x:c>
+      <x:c r="T36" s="66" t="n">
+        <x:v>0.186</x:v>
+      </x:c>
+      <x:c r="U36" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V36" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="62" t="n">
+        <x:v>46143</x:v>
+      </x:c>
+      <x:c r="B37" s="30" t="str">
+        <x:v>Inbound</x:v>
+      </x:c>
+      <x:c r="C37" s="64" t="n">
+        <x:v>5729</x:v>
+      </x:c>
+      <x:c r="D37" s="64" t="n">
+        <x:v>4806</x:v>
+      </x:c>
+      <x:c r="E37" s="64" t="n">
+        <x:v>860</x:v>
+      </x:c>
+      <x:c r="F37" s="66" t="n">
+        <x:v>0.15011345784604643</x:v>
+      </x:c>
+      <x:c r="G37" s="66" t="n">
+        <x:v>0.029940119760478945</x:v>
+      </x:c>
+      <x:c r="H37" s="64" t="n">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="I37" s="66" t="n">
+        <x:v>0.4697674418604651</x:v>
+      </x:c>
+      <x:c r="J37" s="64" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="K37" s="66" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L37" s="64" t="n">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="M37" s="66" t="n">
+        <x:v>0.43023255813953487</x:v>
+      </x:c>
+      <x:c r="N37" s="64" t="n">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="O37" s="66" t="n">
+        <x:v>0.6895348837209302</x:v>
+      </x:c>
+      <x:c r="P37" s="64" t="n">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="Q37" s="66" t="n">
+        <x:v>0.26046511627906976</x:v>
+      </x:c>
+      <x:c r="R37" s="64" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="S37" s="66" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="T37" s="66" t="n">
+        <x:v>0.196</x:v>
+      </x:c>
+      <x:c r="U37" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V37" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="62" t="n">
+        <x:v>46143</x:v>
+      </x:c>
+      <x:c r="B38" s="30" t="str">
+        <x:v>Indirect</x:v>
+      </x:c>
+      <x:c r="C38" s="64" t="n">
+        <x:v>4044</x:v>
+      </x:c>
+      <x:c r="D38" s="64" t="n">
+        <x:v>3325</x:v>
+      </x:c>
+      <x:c r="E38" s="64" t="n">
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="F38" s="66" t="n">
+        <x:v>0.15479723046488625</x:v>
+      </x:c>
+      <x:c r="G38" s="66" t="n">
+        <x:v>0.0313014827018121</x:v>
+      </x:c>
+      <x:c r="H38" s="64" t="n">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="I38" s="66" t="n">
+        <x:v>0.46006389776357826</x:v>
+      </x:c>
+      <x:c r="J38" s="64" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="K38" s="66" t="n">
+        <x:v>0.11022364217252396</x:v>
+      </x:c>
+      <x:c r="L38" s="64" t="n">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="M38" s="66" t="n">
+        <x:v>0.42971246006389774</x:v>
+      </x:c>
+      <x:c r="N38" s="64" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="O38" s="66" t="n">
+        <x:v>0.6805111821086262</x:v>
+      </x:c>
+      <x:c r="P38" s="64" t="n">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="Q38" s="66" t="n">
+        <x:v>0.26996805111821087</x:v>
+      </x:c>
+      <x:c r="R38" s="64" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S38" s="66" t="n">
+        <x:v>0.04952076677316294</x:v>
+      </x:c>
+      <x:c r="T38" s="66" t="n">
+        <x:v>0.186</x:v>
+      </x:c>
+      <x:c r="U38" s="66" t="n">
+        <x:v>0.09999999999999999</x:v>
+      </x:c>
+      <x:c r="V38" s="66" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="62" t="n">
+        <x:v>46143</x:v>
+      </x:c>
+      <x:c r="B39" s="30" t="str">
+        <x:v>OBTM</x:v>
+      </x:c>
+      <x:c r="C39" s="64" t="n">
+        <x:v>3707</x:v>
+      </x:c>
+      <x:c r="D39" s="64" t="n">
+        <x:v>3079</x:v>
+      </x:c>
+      <x:c r="E39" s="64" t="n">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="F39" s="66" t="n">
+        <x:v>0.1516050714863771</x:v>
+      </x:c>
+      <x:c r="G39" s="66" t="n">
+        <x:v>0.0293040293040292</x:v>
+      </x:c>
+      <x:c r="H39" s="64" t="n">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="I39" s="66" t="n">
+        <x:v>0.4697508896797153</x:v>
+      </x:c>
+      <x:c r="J39" s="64" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="K39" s="66" t="n">
+        <x:v>0.099644128113879</x:v>
+      </x:c>
+      <x:c r="L39" s="64" t="n">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="M39" s="66" t="n">
+        <x:v>0.4306049822064057</x:v>
+      </x:c>
+      <x:c r="N39" s="64" t="n">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="O39" s="66" t="n">
+        <x:v>0.6797153024911032</x:v>
+      </x:c>
+      <x:c r="P39" s="64" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="Q39" s="66" t="n">
+        <x:v>0.2704626334519573</x:v>
+      </x:c>
+      <x:c r="R39" s="64" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="S39" s="66" t="n">
+        <x:v>0.0498220640569395</x:v>
+      </x:c>
+      <x:c r="T39" s="66" t="n">
+        <x:v>0.186</x:v>
+      </x:c>
+      <x:c r="U39" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V39" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="62" t="n">
+        <x:v>46143</x:v>
+      </x:c>
+      <x:c r="B40" s="30" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="C40" s="64" t="n">
+        <x:v>2696</x:v>
+      </x:c>
+      <x:c r="D40" s="64" t="n">
+        <x:v>2195</x:v>
+      </x:c>
+      <x:c r="E40" s="64" t="n">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="F40" s="66" t="n">
+        <x:v>0.1531899109792285</x:v>
+      </x:c>
+      <x:c r="G40" s="66" t="n">
+        <x:v>0.029925187032418865</x:v>
+      </x:c>
+      <x:c r="H40" s="64" t="n">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="I40" s="66" t="n">
+        <x:v>0.4794188861985472</x:v>
+      </x:c>
+      <x:c r="J40" s="64" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K40" s="66" t="n">
+        <x:v>0.08958837772397095</x:v>
+      </x:c>
+      <x:c r="L40" s="64" t="n">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="M40" s="66" t="n">
+        <x:v>0.43099273607748184</x:v>
+      </x:c>
+      <x:c r="N40" s="64" t="n">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="O40" s="66" t="n">
+        <x:v>0.6707021791767555</x:v>
+      </x:c>
+      <x:c r="P40" s="64" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="Q40" s="66" t="n">
+        <x:v>0.28087167070217917</x:v>
+      </x:c>
+      <x:c r="R40" s="64" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="S40" s="66" t="n">
+        <x:v>0.048426150121065374</x:v>
+      </x:c>
+      <x:c r="T40" s="66" t="n">
+        <x:v>0.186</x:v>
+      </x:c>
+      <x:c r="U40" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V40" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="62" t="n">
+        <x:v>46174</x:v>
+      </x:c>
+      <x:c r="B41" s="30" t="str">
+        <x:v>D2D</x:v>
+      </x:c>
+      <x:c r="C41" s="64" t="n">
+        <x:v>6960</x:v>
+      </x:c>
+      <x:c r="D41" s="64" t="n">
+        <x:v>5663</x:v>
+      </x:c>
+      <x:c r="E41" s="64" t="n">
+        <x:v>1085</x:v>
+      </x:c>
+      <x:c r="F41" s="66" t="n">
+        <x:v>0.15589080459770116</x:v>
+      </x:c>
+      <x:c r="G41" s="66" t="n">
+        <x:v>0.03038936372269707</x:v>
+      </x:c>
+      <x:c r="H41" s="64" t="n">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="I41" s="66" t="n">
+        <x:v>0.4700460829493088</x:v>
+      </x:c>
+      <x:c r="J41" s="64" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="K41" s="66" t="n">
+        <x:v>0.09032258064516129</x:v>
+      </x:c>
+      <x:c r="L41" s="64" t="n">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="M41" s="66" t="n">
+        <x:v>0.4396313364055299</x:v>
+      </x:c>
+      <x:c r="N41" s="64" t="n">
+        <x:v>738</x:v>
+      </x:c>
+      <x:c r="O41" s="66" t="n">
+        <x:v>0.680184331797235</x:v>
+      </x:c>
+      <x:c r="P41" s="64" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="Q41" s="66" t="n">
+        <x:v>0.27004608294930876</x:v>
+      </x:c>
+      <x:c r="R41" s="64" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="S41" s="66" t="n">
+        <x:v>0.04976958525345622</x:v>
+      </x:c>
+      <x:c r="T41" s="66" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="U41" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V41" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="62" t="n">
+        <x:v>46174</x:v>
+      </x:c>
+      <x:c r="B42" s="30" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="C42" s="64" t="n">
+        <x:v>6264</x:v>
+      </x:c>
+      <x:c r="D42" s="64" t="n">
+        <x:v>5356</x:v>
+      </x:c>
+      <x:c r="E42" s="64" t="n">
+        <x:v>891</x:v>
+      </x:c>
+      <x:c r="F42" s="66" t="n">
+        <x:v>0.14224137931034483</x:v>
+      </x:c>
+      <x:c r="G42" s="66" t="n">
+        <x:v>0.03005780346820819</x:v>
+      </x:c>
+      <x:c r="H42" s="64" t="n">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="I42" s="66" t="n">
+        <x:v>0.4904601571268238</x:v>
+      </x:c>
+      <x:c r="J42" s="64" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K42" s="66" t="n">
+        <x:v>0.08978675645342311</x:v>
+      </x:c>
+      <x:c r="L42" s="64" t="n">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="M42" s="66" t="n">
+        <x:v>0.41975308641975306</x:v>
+      </x:c>
+      <x:c r="N42" s="64" t="n">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="O42" s="66" t="n">
+        <x:v>0.6599326599326599</x:v>
+      </x:c>
+      <x:c r="P42" s="64" t="n">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="Q42" s="66" t="n">
+        <x:v>0.2895622895622896</x:v>
+      </x:c>
+      <x:c r="R42" s="64" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="S42" s="66" t="n">
+        <x:v>0.050505050505050504</x:v>
+      </x:c>
+      <x:c r="T42" s="66" t="n">
+        <x:v>0.19</x:v>
+      </x:c>
+      <x:c r="U42" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V42" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="62" t="n">
+        <x:v>46174</x:v>
+      </x:c>
+      <x:c r="B43" s="30" t="str">
+        <x:v>Digital Partner</x:v>
+      </x:c>
+      <x:c r="C43" s="64" t="n">
+        <x:v>4872</x:v>
+      </x:c>
+      <x:c r="D43" s="64" t="n">
+        <x:v>4045</x:v>
+      </x:c>
+      <x:c r="E43" s="64" t="n">
+        <x:v>745</x:v>
+      </x:c>
+      <x:c r="F43" s="66" t="n">
+        <x:v>0.15291461412151067</x:v>
+      </x:c>
+      <x:c r="G43" s="66" t="n">
+        <x:v>0.030428769017980528</x:v>
+      </x:c>
+      <x:c r="H43" s="64" t="n">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="I43" s="66" t="n">
+        <x:v>0.48053691275167787</x:v>
+      </x:c>
+      <x:c r="J43" s="64" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="K43" s="66" t="n">
+        <x:v>0.08993288590604027</x:v>
+      </x:c>
+      <x:c r="L43" s="64" t="n">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="M43" s="66" t="n">
+        <x:v>0.42953020134228187</x:v>
+      </x:c>
+      <x:c r="N43" s="64" t="n">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="O43" s="66" t="n">
+        <x:v>0.6697986577181209</x:v>
+      </x:c>
+      <x:c r="P43" s="64" t="n">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="Q43" s="66" t="n">
+        <x:v>0.28053691275167786</x:v>
+      </x:c>
+      <x:c r="R43" s="64" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="S43" s="66" t="n">
+        <x:v>0.049664429530201344</x:v>
+      </x:c>
+      <x:c r="T43" s="66" t="n">
+        <x:v>0.19</x:v>
+      </x:c>
+      <x:c r="U43" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V43" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="62" t="n">
+        <x:v>46174</x:v>
+      </x:c>
+      <x:c r="B44" s="30" t="str">
+        <x:v>Inbound</x:v>
+      </x:c>
+      <x:c r="C44" s="64" t="n">
+        <x:v>5916</x:v>
+      </x:c>
+      <x:c r="D44" s="64" t="n">
+        <x:v>4961</x:v>
+      </x:c>
+      <x:c r="E44" s="64" t="n">
+        <x:v>886</x:v>
+      </x:c>
+      <x:c r="F44" s="66" t="n">
+        <x:v>0.149763353617309</x:v>
+      </x:c>
+      <x:c r="G44" s="66" t="n">
+        <x:v>0.03023255813953485</x:v>
+      </x:c>
+      <x:c r="H44" s="64" t="n">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="I44" s="66" t="n">
+        <x:v>0.4796839729119639</x:v>
+      </x:c>
+      <x:c r="J44" s="64" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K44" s="66" t="n">
+        <x:v>0.09029345372460497</x:v>
+      </x:c>
+      <x:c r="L44" s="64" t="n">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="M44" s="66" t="n">
+        <x:v>0.43002257336343114</x:v>
+      </x:c>
+      <x:c r="N44" s="64" t="n">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="O44" s="66" t="n">
+        <x:v>0.6794582392776524</x:v>
+      </x:c>
+      <x:c r="P44" s="64" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="Q44" s="66" t="n">
+        <x:v>0.2697516930022573</x:v>
+      </x:c>
+      <x:c r="R44" s="64" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="S44" s="66" t="n">
+        <x:v>0.050790067720090294</x:v>
+      </x:c>
+      <x:c r="T44" s="66" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="U44" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V44" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="62" t="n">
+        <x:v>46174</x:v>
+      </x:c>
+      <x:c r="B45" s="30" t="str">
+        <x:v>Indirect</x:v>
+      </x:c>
+      <x:c r="C45" s="64" t="n">
+        <x:v>4176</x:v>
+      </x:c>
+      <x:c r="D45" s="64" t="n">
+        <x:v>3432</x:v>
+      </x:c>
+      <x:c r="E45" s="64" t="n">
+        <x:v>644</x:v>
+      </x:c>
+      <x:c r="F45" s="66" t="n">
+        <x:v>0.15421455938697318</x:v>
+      </x:c>
+      <x:c r="G45" s="66" t="n">
+        <x:v>0.028753993610223683</x:v>
+      </x:c>
+      <x:c r="H45" s="64" t="n">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="I45" s="66" t="n">
+        <x:v>0.4704968944099379</x:v>
+      </x:c>
+      <x:c r="J45" s="64" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="K45" s="66" t="n">
+        <x:v>0.09937888198757763</x:v>
+      </x:c>
+      <x:c r="L45" s="64" t="n">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="M45" s="66" t="n">
+        <x:v>0.4301242236024845</x:v>
+      </x:c>
+      <x:c r="N45" s="64" t="n">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="O45" s="66" t="n">
+        <x:v>0.6692546583850931</x:v>
+      </x:c>
+      <x:c r="P45" s="64" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="Q45" s="66" t="n">
+        <x:v>0.2795031055900621</x:v>
+      </x:c>
+      <x:c r="R45" s="64" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S45" s="66" t="n">
+        <x:v>0.05124223602484472</x:v>
+      </x:c>
+      <x:c r="T45" s="66" t="n">
+        <x:v>0.19</x:v>
+      </x:c>
+      <x:c r="U45" s="66" t="n">
+        <x:v>0.09999999999999999</x:v>
+      </x:c>
+      <x:c r="V45" s="66" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="62" t="n">
+        <x:v>46174</x:v>
+      </x:c>
+      <x:c r="B46" s="30" t="str">
+        <x:v>OBTM</x:v>
+      </x:c>
+      <x:c r="C46" s="64" t="n">
+        <x:v>3828</x:v>
+      </x:c>
+      <x:c r="D46" s="64" t="n">
+        <x:v>3178</x:v>
+      </x:c>
+      <x:c r="E46" s="64" t="n">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="F46" s="66" t="n">
+        <x:v>0.15125391849529782</x:v>
+      </x:c>
+      <x:c r="G46" s="66" t="n">
+        <x:v>0.030249110320284656</x:v>
+      </x:c>
+      <x:c r="H46" s="64" t="n">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="I46" s="66" t="n">
+        <x:v>0.48013816925734026</x:v>
+      </x:c>
+      <x:c r="J46" s="64" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="K46" s="66" t="n">
+        <x:v>0.08981001727115717</x:v>
+      </x:c>
+      <x:c r="L46" s="64" t="n">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="M46" s="66" t="n">
+        <x:v>0.43005181347150256</x:v>
+      </x:c>
+      <x:c r="N46" s="64" t="n">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="O46" s="66" t="n">
+        <x:v>0.6701208981001727</x:v>
+      </x:c>
+      <x:c r="P46" s="64" t="n">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="Q46" s="66" t="n">
+        <x:v>0.27979274611398963</x:v>
+      </x:c>
+      <x:c r="R46" s="64" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="S46" s="66" t="n">
+        <x:v>0.05008635578583765</x:v>
+      </x:c>
+      <x:c r="T46" s="66" t="n">
+        <x:v>0.19</x:v>
+      </x:c>
+      <x:c r="U46" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V46" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="62" t="n">
+        <x:v>46174</x:v>
+      </x:c>
+      <x:c r="B47" s="30" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="C47" s="64" t="n">
+        <x:v>2784</x:v>
+      </x:c>
+      <x:c r="D47" s="64" t="n">
+        <x:v>2265</x:v>
+      </x:c>
+      <x:c r="E47" s="64" t="n">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="F47" s="66" t="n">
+        <x:v>0.1526580459770115</x:v>
+      </x:c>
+      <x:c r="G47" s="66" t="n">
+        <x:v>0.029055690072639306</x:v>
+      </x:c>
+      <x:c r="H47" s="64" t="n">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="I47" s="66" t="n">
+        <x:v>0.4894117647058824</x:v>
+      </x:c>
+      <x:c r="J47" s="64" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="K47" s="66" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="L47" s="64" t="n">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="M47" s="66" t="n">
+        <x:v>0.43058823529411766</x:v>
+      </x:c>
+      <x:c r="N47" s="64" t="n">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="O47" s="66" t="n">
+        <x:v>0.6588235294117647</x:v>
+      </x:c>
+      <x:c r="P47" s="64" t="n">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="Q47" s="66" t="n">
+        <x:v>0.28941176470588237</x:v>
+      </x:c>
+      <x:c r="R47" s="64" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="S47" s="66" t="n">
+        <x:v>0.05176470588235294</x:v>
+      </x:c>
+      <x:c r="T47" s="66" t="n">
+        <x:v>0.19</x:v>
+      </x:c>
+      <x:c r="U47" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V47" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="62" t="n">
+        <x:v>46204</x:v>
+      </x:c>
+      <x:c r="B48" s="30" t="str">
+        <x:v>D2D</x:v>
+      </x:c>
+      <x:c r="C48" s="64" t="n">
+        <x:v>7160</x:v>
+      </x:c>
+      <x:c r="D48" s="64" t="n">
+        <x:v>5819</x:v>
+      </x:c>
+      <x:c r="E48" s="64" t="n">
+        <x:v>1117</x:v>
+      </x:c>
+      <x:c r="F48" s="66" t="n">
+        <x:v>0.15600558659217878</x:v>
+      </x:c>
+      <x:c r="G48" s="66" t="n">
+        <x:v>0.029493087557603603</x:v>
+      </x:c>
+      <x:c r="H48" s="64" t="n">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="I48" s="66" t="n">
+        <x:v>0.4601611459265891</x:v>
+      </x:c>
+      <x:c r="J48" s="64" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="K48" s="66" t="n">
+        <x:v>0.10026857654431513</x:v>
+      </x:c>
+      <x:c r="L48" s="64" t="n">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="M48" s="66" t="n">
+        <x:v>0.4395702775290958</x:v>
+      </x:c>
+      <x:c r="N48" s="64" t="n">
+        <x:v>771</x:v>
+      </x:c>
+      <x:c r="O48" s="66" t="n">
+        <x:v>0.6902417188898836</x:v>
+      </x:c>
+      <x:c r="P48" s="64" t="n">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="Q48" s="66" t="n">
+        <x:v>0.25962399283795884</x:v>
+      </x:c>
+      <x:c r="R48" s="64" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="S48" s="66" t="n">
+        <x:v>0.050134288272157566</x:v>
+      </x:c>
+      <x:c r="T48" s="66" t="n">
+        <x:v>0.20400000000000001</x:v>
+      </x:c>
+      <x:c r="U48" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V48" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="62" t="n">
+        <x:v>46204</x:v>
+      </x:c>
+      <x:c r="B49" s="30" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="C49" s="64" t="n">
+        <x:v>6444</x:v>
+      </x:c>
+      <x:c r="D49" s="64" t="n">
+        <x:v>5505</x:v>
+      </x:c>
+      <x:c r="E49" s="64" t="n">
+        <x:v>918</x:v>
+      </x:c>
+      <x:c r="F49" s="66" t="n">
+        <x:v>0.1424581005586592</x:v>
+      </x:c>
+      <x:c r="G49" s="66" t="n">
+        <x:v>0.030303030303030276</x:v>
+      </x:c>
+      <x:c r="H49" s="64" t="n">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="I49" s="66" t="n">
+        <x:v>0.4803921568627451</x:v>
+      </x:c>
+      <x:c r="J49" s="64" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K49" s="66" t="n">
+        <x:v>0.10021786492374728</x:v>
+      </x:c>
+      <x:c r="L49" s="64" t="n">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="M49" s="66" t="n">
+        <x:v>0.41938997821350765</x:v>
+      </x:c>
+      <x:c r="N49" s="64" t="n">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="O49" s="66" t="n">
+        <x:v>0.6699346405228758</x:v>
+      </x:c>
+      <x:c r="P49" s="64" t="n">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="Q49" s="66" t="n">
+        <x:v>0.27995642701525053</x:v>
+      </x:c>
+      <x:c r="R49" s="64" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="S49" s="66" t="n">
+        <x:v>0.05010893246187364</x:v>
+      </x:c>
+      <x:c r="T49" s="66" t="n">
+        <x:v>0.194</x:v>
+      </x:c>
+      <x:c r="U49" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V49" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="62" t="n">
+        <x:v>46204</x:v>
+      </x:c>
+      <x:c r="B50" s="30" t="str">
+        <x:v>Digital Partner</x:v>
+      </x:c>
+      <x:c r="C50" s="64" t="n">
+        <x:v>5012</x:v>
+      </x:c>
+      <x:c r="D50" s="64" t="n">
+        <x:v>4157</x:v>
+      </x:c>
+      <x:c r="E50" s="64" t="n">
+        <x:v>767</x:v>
+      </x:c>
+      <x:c r="F50" s="66" t="n">
+        <x:v>0.15303272146847566</x:v>
+      </x:c>
+      <x:c r="G50" s="66" t="n">
+        <x:v>0.029530201342281792</x:v>
+      </x:c>
+      <x:c r="H50" s="64" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="I50" s="66" t="n">
+        <x:v>0.46936114732724904</x:v>
+      </x:c>
+      <x:c r="J50" s="64" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="K50" s="66" t="n">
+        <x:v>0.10039113428943937</x:v>
+      </x:c>
+      <x:c r="L50" s="64" t="n">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="M50" s="66" t="n">
+        <x:v>0.4302477183833116</x:v>
+      </x:c>
+      <x:c r="N50" s="64" t="n">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="O50" s="66" t="n">
+        <x:v>0.6805736636245111</x:v>
+      </x:c>
+      <x:c r="P50" s="64" t="n">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="Q50" s="66" t="n">
+        <x:v>0.26988265971316816</x:v>
+      </x:c>
+      <x:c r="R50" s="64" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="S50" s="66" t="n">
+        <x:v>0.04954367666232073</x:v>
+      </x:c>
+      <x:c r="T50" s="66" t="n">
+        <x:v>0.194</x:v>
+      </x:c>
+      <x:c r="U50" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V50" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="62" t="n">
+        <x:v>46204</x:v>
+      </x:c>
+      <x:c r="B51" s="30" t="str">
+        <x:v>Inbound</x:v>
+      </x:c>
+      <x:c r="C51" s="64" t="n">
+        <x:v>6086</x:v>
+      </x:c>
+      <x:c r="D51" s="64" t="n">
+        <x:v>5098</x:v>
+      </x:c>
+      <x:c r="E51" s="64" t="n">
+        <x:v>913</x:v>
+      </x:c>
+      <x:c r="F51" s="66" t="n">
+        <x:v>0.15001643115346697</x:v>
+      </x:c>
+      <x:c r="G51" s="66" t="n">
+        <x:v>0.030474040632054278</x:v>
+      </x:c>
+      <x:c r="H51" s="64" t="n">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="I51" s="66" t="n">
+        <x:v>0.46987951807228917</x:v>
+      </x:c>
+      <x:c r="J51" s="64" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="K51" s="66" t="n">
+        <x:v>0.09967141292442497</x:v>
+      </x:c>
+      <x:c r="L51" s="64" t="n">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="M51" s="66" t="n">
+        <x:v>0.4304490690032859</x:v>
+      </x:c>
+      <x:c r="N51" s="64" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="O51" s="66" t="n">
+        <x:v>0.6900328587075575</x:v>
+      </x:c>
+      <x:c r="P51" s="64" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="Q51" s="66" t="n">
+        <x:v>0.25958378970427165</x:v>
+      </x:c>
+      <x:c r="R51" s="64" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="S51" s="66" t="n">
+        <x:v>0.050383351588170866</x:v>
+      </x:c>
+      <x:c r="T51" s="66" t="n">
+        <x:v>0.20400000000000001</x:v>
+      </x:c>
+      <x:c r="U51" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V51" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="62" t="n">
+        <x:v>46204</x:v>
+      </x:c>
+      <x:c r="B52" s="30" t="str">
+        <x:v>Indirect</x:v>
+      </x:c>
+      <x:c r="C52" s="64" t="n">
+        <x:v>4296</x:v>
+      </x:c>
+      <x:c r="D52" s="64" t="n">
+        <x:v>3527</x:v>
+      </x:c>
+      <x:c r="E52" s="64" t="n">
+        <x:v>664</x:v>
+      </x:c>
+      <x:c r="F52" s="66" t="n">
+        <x:v>0.15456238361266295</x:v>
+      </x:c>
+      <x:c r="G52" s="66" t="n">
+        <x:v>0.03105590062111796</x:v>
+      </x:c>
+      <x:c r="H52" s="64" t="n">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="I52" s="66" t="n">
+        <x:v>0.45933734939759036</x:v>
+      </x:c>
+      <x:c r="J52" s="64" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="K52" s="66" t="n">
+        <x:v>0.10993975903614457</x:v>
+      </x:c>
+      <x:c r="L52" s="64" t="n">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="M52" s="66" t="n">
+        <x:v>0.4307228915662651</x:v>
+      </x:c>
+      <x:c r="N52" s="64" t="n">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="O52" s="66" t="n">
+        <x:v>0.6807228915662651</x:v>
+      </x:c>
+      <x:c r="P52" s="64" t="n">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="Q52" s="66" t="n">
+        <x:v>0.26957831325301207</x:v>
+      </x:c>
+      <x:c r="R52" s="64" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S52" s="66" t="n">
+        <x:v>0.04969879518072289</x:v>
+      </x:c>
+      <x:c r="T52" s="66" t="n">
+        <x:v>0.194</x:v>
+      </x:c>
+      <x:c r="U52" s="66" t="n">
+        <x:v>0.09999999999999999</x:v>
+      </x:c>
+      <x:c r="V52" s="66" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="62" t="n">
+        <x:v>46204</x:v>
+      </x:c>
+      <x:c r="B53" s="30" t="str">
+        <x:v>OBTM</x:v>
+      </x:c>
+      <x:c r="C53" s="64" t="n">
+        <x:v>3938</x:v>
+      </x:c>
+      <x:c r="D53" s="64" t="n">
+        <x:v>3266</x:v>
+      </x:c>
+      <x:c r="E53" s="64" t="n">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="F53" s="66" t="n">
+        <x:v>0.15134586084306756</x:v>
+      </x:c>
+      <x:c r="G53" s="66" t="n">
+        <x:v>0.029360967184801412</x:v>
+      </x:c>
+      <x:c r="H53" s="64" t="n">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="I53" s="66" t="n">
+        <x:v>0.4697986577181208</x:v>
+      </x:c>
+      <x:c r="J53" s="64" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K53" s="66" t="n">
+        <x:v>0.10067114093959731</x:v>
+      </x:c>
+      <x:c r="L53" s="64" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="M53" s="66" t="n">
+        <x:v>0.42953020134228187</x:v>
+      </x:c>
+      <x:c r="N53" s="64" t="n">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="O53" s="66" t="n">
+        <x:v>0.6795302013422819</x:v>
+      </x:c>
+      <x:c r="P53" s="64" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="Q53" s="66" t="n">
+        <x:v>0.2701342281879195</x:v>
+      </x:c>
+      <x:c r="R53" s="64" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="S53" s="66" t="n">
+        <x:v>0.050335570469798654</x:v>
+      </x:c>
+      <x:c r="T53" s="66" t="n">
+        <x:v>0.194</x:v>
+      </x:c>
+      <x:c r="U53" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V53" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="62" t="n">
+        <x:v>46204</x:v>
+      </x:c>
+      <x:c r="B54" s="30" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="C54" s="64" t="n">
+        <x:v>2864</x:v>
+      </x:c>
+      <x:c r="D54" s="64" t="n">
+        <x:v>2328</x:v>
+      </x:c>
+      <x:c r="E54" s="64" t="n">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="F54" s="66" t="n">
+        <x:v>0.15293296089385475</x:v>
+      </x:c>
+      <x:c r="G54" s="66" t="n">
+        <x:v>0.030588235294117583</x:v>
+      </x:c>
+      <x:c r="H54" s="64" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="I54" s="66" t="n">
+        <x:v>0.4794520547945205</x:v>
+      </x:c>
+      <x:c r="J54" s="64" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="K54" s="66" t="n">
+        <x:v>0.08904109589041095</x:v>
+      </x:c>
+      <x:c r="L54" s="64" t="n">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="M54" s="66" t="n">
+        <x:v>0.4315068493150685</x:v>
+      </x:c>
+      <x:c r="N54" s="64" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="O54" s="66" t="n">
+        <x:v>0.6689497716894978</x:v>
+      </x:c>
+      <x:c r="P54" s="64" t="n">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="Q54" s="66" t="n">
+        <x:v>0.2808219178082192</x:v>
+      </x:c>
+      <x:c r="R54" s="64" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="S54" s="66" t="n">
+        <x:v>0.0502283105022831</x:v>
+      </x:c>
+      <x:c r="T54" s="66" t="n">
+        <x:v>0.194</x:v>
+      </x:c>
+      <x:c r="U54" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V54" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="62" t="n">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="B55" s="30" t="str">
+        <x:v>D2D</x:v>
+      </x:c>
+      <x:c r="C55" s="64" t="n">
+        <x:v>7360</x:v>
+      </x:c>
+      <x:c r="D55" s="64" t="n">
+        <x:v>5957</x:v>
+      </x:c>
+      <x:c r="E55" s="64" t="n">
+        <x:v>1149</x:v>
+      </x:c>
+      <x:c r="F55" s="66" t="n">
+        <x:v>0.15611413043478262</x:v>
+      </x:c>
+      <x:c r="G55" s="66" t="n">
+        <x:v>0.0286481647269472</x:v>
+      </x:c>
+      <x:c r="H55" s="64" t="n">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="I55" s="66" t="n">
+        <x:v>0.4699738903394256</x:v>
+      </x:c>
+      <x:c r="J55" s="64" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="K55" s="66" t="n">
+        <x:v>0.10008703220191471</x:v>
+      </x:c>
+      <x:c r="L55" s="64" t="n">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="M55" s="66" t="n">
+        <x:v>0.4299390774586597</x:v>
+      </x:c>
+      <x:c r="N55" s="64" t="n">
+        <x:v>793</x:v>
+      </x:c>
+      <x:c r="O55" s="66" t="n">
+        <x:v>0.6901653611836379</x:v>
+      </x:c>
+      <x:c r="P55" s="64" t="n">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="Q55" s="66" t="n">
+        <x:v>0.26022628372497825</x:v>
+      </x:c>
+      <x:c r="R55" s="64" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="S55" s="66" t="n">
+        <x:v>0.04960835509138381</x:v>
+      </x:c>
+      <x:c r="T55" s="66" t="n">
+        <x:v>0.20800000000000002</x:v>
+      </x:c>
+      <x:c r="U55" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V55" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="62" t="n">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="B56" s="30" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="C56" s="64" t="n">
+        <x:v>6624</x:v>
+      </x:c>
+      <x:c r="D56" s="64" t="n">
+        <x:v>5634</x:v>
+      </x:c>
+      <x:c r="E56" s="64" t="n">
+        <x:v>944</x:v>
+      </x:c>
+      <x:c r="F56" s="66" t="n">
+        <x:v>0.14251207729468598</x:v>
+      </x:c>
+      <x:c r="G56" s="66" t="n">
+        <x:v>0.028322440087146017</x:v>
+      </x:c>
+      <x:c r="H56" s="64" t="n">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="I56" s="66" t="n">
+        <x:v>0.4904661016949153</x:v>
+      </x:c>
+      <x:c r="J56" s="64" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="K56" s="66" t="n">
+        <x:v>0.09957627118644068</x:v>
+      </x:c>
+      <x:c r="L56" s="64" t="n">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="M56" s="66" t="n">
+        <x:v>0.4099576271186441</x:v>
+      </x:c>
+      <x:c r="N56" s="64" t="n">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="O56" s="66" t="n">
+        <x:v>0.6694915254237288</x:v>
+      </x:c>
+      <x:c r="P56" s="64" t="n">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="Q56" s="66" t="n">
+        <x:v>0.2796610169491525</x:v>
+      </x:c>
+      <x:c r="R56" s="64" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="S56" s="66" t="n">
+        <x:v>0.05084745762711865</x:v>
+      </x:c>
+      <x:c r="T56" s="66" t="n">
+        <x:v>0.198</x:v>
+      </x:c>
+      <x:c r="U56" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V56" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="62" t="n">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="B57" s="30" t="str">
+        <x:v>Digital Partner</x:v>
+      </x:c>
+      <x:c r="C57" s="64" t="n">
+        <x:v>5152</x:v>
+      </x:c>
+      <x:c r="D57" s="64" t="n">
+        <x:v>4255</x:v>
+      </x:c>
+      <x:c r="E57" s="64" t="n">
+        <x:v>789</x:v>
+      </x:c>
+      <x:c r="F57" s="66" t="n">
+        <x:v>0.1531444099378882</x:v>
+      </x:c>
+      <x:c r="G57" s="66" t="n">
+        <x:v>0.028683181225554133</x:v>
+      </x:c>
+      <x:c r="H57" s="64" t="n">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="I57" s="66" t="n">
+        <x:v>0.4803548795944233</x:v>
+      </x:c>
+      <x:c r="J57" s="64" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="K57" s="66" t="n">
+        <x:v>0.10012674271229405</x:v>
+      </x:c>
+      <x:c r="L57" s="64" t="n">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="M57" s="66" t="n">
+        <x:v>0.41951837769328265</x:v>
+      </x:c>
+      <x:c r="N57" s="64" t="n">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="O57" s="66" t="n">
+        <x:v>0.6806083650190115</x:v>
+      </x:c>
+      <x:c r="P57" s="64" t="n">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="Q57" s="66" t="n">
+        <x:v>0.26996197718631176</x:v>
+      </x:c>
+      <x:c r="R57" s="64" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="S57" s="66" t="n">
+        <x:v>0.049429657794676805</x:v>
+      </x:c>
+      <x:c r="T57" s="66" t="n">
+        <x:v>0.198</x:v>
+      </x:c>
+      <x:c r="U57" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V57" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="62" t="n">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="B58" s="30" t="str">
+        <x:v>Inbound</x:v>
+      </x:c>
+      <x:c r="C58" s="64" t="n">
+        <x:v>6256</x:v>
+      </x:c>
+      <x:c r="D58" s="64" t="n">
+        <x:v>5218</x:v>
+      </x:c>
+      <x:c r="E58" s="64" t="n">
+        <x:v>939</x:v>
+      </x:c>
+      <x:c r="F58" s="66" t="n">
+        <x:v>0.15009590792838876</x:v>
+      </x:c>
+      <x:c r="G58" s="66" t="n">
+        <x:v>0.028477546549835697</x:v>
+      </x:c>
+      <x:c r="H58" s="64" t="n">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="I58" s="66" t="n">
+        <x:v>0.4802981895633653</x:v>
+      </x:c>
+      <x:c r="J58" s="64" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="K58" s="66" t="n">
+        <x:v>0.10010649627263046</x:v>
+      </x:c>
+      <x:c r="L58" s="64" t="n">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="M58" s="66" t="n">
+        <x:v>0.41959531416400425</x:v>
+      </x:c>
+      <x:c r="N58" s="64" t="n">
+        <x:v>648</x:v>
+      </x:c>
+      <x:c r="O58" s="66" t="n">
+        <x:v>0.6900958466453674</x:v>
+      </x:c>
+      <x:c r="P58" s="64" t="n">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="Q58" s="66" t="n">
+        <x:v>0.2598509052183174</x:v>
+      </x:c>
+      <x:c r="R58" s="64" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="S58" s="66" t="n">
+        <x:v>0.05005324813631523</x:v>
+      </x:c>
+      <x:c r="T58" s="66" t="n">
+        <x:v>0.20800000000000002</x:v>
+      </x:c>
+      <x:c r="U58" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V58" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="62" t="n">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="B59" s="30" t="str">
+        <x:v>Indirect</x:v>
+      </x:c>
+      <x:c r="C59" s="64" t="n">
+        <x:v>4416</x:v>
+      </x:c>
+      <x:c r="D59" s="64" t="n">
+        <x:v>3610</x:v>
+      </x:c>
+      <x:c r="E59" s="64" t="n">
+        <x:v>683</x:v>
+      </x:c>
+      <x:c r="F59" s="66" t="n">
+        <x:v>0.15466485507246377</x:v>
+      </x:c>
+      <x:c r="G59" s="66" t="n">
+        <x:v>0.028614457831325213</x:v>
+      </x:c>
+      <x:c r="H59" s="64" t="n">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="I59" s="66" t="n">
+        <x:v>0.4699853587115666</x:v>
+      </x:c>
+      <x:c r="J59" s="64" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="K59" s="66" t="n">
+        <x:v>0.10980966325036604</x:v>
+      </x:c>
+      <x:c r="L59" s="64" t="n">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="M59" s="66" t="n">
+        <x:v>0.42020497803806733</x:v>
+      </x:c>
+      <x:c r="N59" s="64" t="n">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="O59" s="66" t="n">
+        <x:v>0.6793557833089312</x:v>
+      </x:c>
+      <x:c r="P59" s="64" t="n">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="Q59" s="66" t="n">
+        <x:v>0.26939970717423134</x:v>
+      </x:c>
+      <x:c r="R59" s="64" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="S59" s="66" t="n">
+        <x:v>0.05124450951683748</x:v>
+      </x:c>
+      <x:c r="T59" s="66" t="n">
+        <x:v>0.198</x:v>
+      </x:c>
+      <x:c r="U59" s="66" t="n">
+        <x:v>0.09999999999999999</x:v>
+      </x:c>
+      <x:c r="V59" s="66" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="62" t="n">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="B60" s="30" t="str">
+        <x:v>OBTM</x:v>
+      </x:c>
+      <x:c r="C60" s="64" t="n">
+        <x:v>4048</x:v>
+      </x:c>
+      <x:c r="D60" s="64" t="n">
+        <x:v>3343</x:v>
+      </x:c>
+      <x:c r="E60" s="64" t="n">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="F60" s="66" t="n">
+        <x:v>0.15143280632411066</x:v>
+      </x:c>
+      <x:c r="G60" s="66" t="n">
+        <x:v>0.028523489932885893</x:v>
+      </x:c>
+      <x:c r="H60" s="64" t="n">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="I60" s="66" t="n">
+        <x:v>0.4796084828711256</x:v>
+      </x:c>
+      <x:c r="J60" s="64" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K60" s="66" t="n">
+        <x:v>0.09951060358890701</x:v>
+      </x:c>
+      <x:c r="L60" s="64" t="n">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="M60" s="66" t="n">
+        <x:v>0.42088091353996737</x:v>
+      </x:c>
+      <x:c r="N60" s="64" t="n">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="O60" s="66" t="n">
+        <x:v>0.6802610114192496</x:v>
+      </x:c>
+      <x:c r="P60" s="64" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="Q60" s="66" t="n">
+        <x:v>0.2707993474714519</x:v>
+      </x:c>
+      <x:c r="R60" s="64" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="S60" s="66" t="n">
+        <x:v>0.048939641109298535</x:v>
+      </x:c>
+      <x:c r="T60" s="66" t="n">
+        <x:v>0.198</x:v>
+      </x:c>
+      <x:c r="U60" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V60" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="62" t="n">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="B61" s="30" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="C61" s="64" t="n">
+        <x:v>2944</x:v>
+      </x:c>
+      <x:c r="D61" s="64" t="n">
+        <x:v>2383</x:v>
+      </x:c>
+      <x:c r="E61" s="64" t="n">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="F61" s="66" t="n">
+        <x:v>0.1531929347826087</x:v>
+      </x:c>
+      <x:c r="G61" s="66" t="n">
+        <x:v>0.029680365296803624</x:v>
+      </x:c>
+      <x:c r="H61" s="64" t="n">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="I61" s="66" t="n">
+        <x:v>0.49002217294900224</x:v>
+      </x:c>
+      <x:c r="J61" s="64" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K61" s="66" t="n">
+        <x:v>0.09090909090909091</x:v>
+      </x:c>
+      <x:c r="L61" s="64" t="n">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="M61" s="66" t="n">
+        <x:v>0.4190687361419069</x:v>
+      </x:c>
+      <x:c r="N61" s="64" t="n">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="O61" s="66" t="n">
+        <x:v>0.6696230598669624</x:v>
+      </x:c>
+      <x:c r="P61" s="64" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="Q61" s="66" t="n">
+        <x:v>0.2793791574279379</x:v>
+      </x:c>
+      <x:c r="R61" s="64" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S61" s="66" t="n">
+        <x:v>0.050997782705099776</x:v>
+      </x:c>
+      <x:c r="T61" s="66" t="n">
+        <x:v>0.198</x:v>
+      </x:c>
+      <x:c r="U61" s="66" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V61" s="66" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="117" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="B62" s="118" t="str">
+        <x:v>D2D</x:v>
+      </x:c>
+      <x:c r="C62" s="119" t="n">
+        <x:v>7805</x:v>
+      </x:c>
+      <x:c r="D62" s="119" t="n">
+        <x:v>5897</x:v>
+      </x:c>
+      <x:c r="E62" s="119" t="n">
+        <x:v>1516</x:v>
+      </x:c>
+      <x:c r="F62" s="120" t="n">
+        <x:v>0.194234465086483</x:v>
+      </x:c>
+      <x:c r="G62" s="120" t="n">
+        <x:v>0.31940818102698</x:v>
+      </x:c>
+      <x:c r="H62" s="119" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="I62" s="120" t="n">
+        <x:v>0.32981530343007914</x:v>
+      </x:c>
+      <x:c r="J62" s="119" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="K62" s="120" t="n">
+        <x:v>0.08970976253298153</x:v>
+      </x:c>
+      <x:c r="L62" s="119" t="n">
+        <x:v>880</x:v>
+      </x:c>
+      <x:c r="M62" s="120" t="n">
+        <x:v>0.5804749340369393</x:v>
+      </x:c>
+      <x:c r="N62" s="119" t="n">
+        <x:v>1092</x:v>
+      </x:c>
+      <x:c r="O62" s="120" t="n">
+        <x:v>0.7203166226912929</x:v>
+      </x:c>
+      <x:c r="P62" s="119" t="n">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="Q62" s="120" t="n">
+        <x:v>0.23021108179419525</x:v>
+      </x:c>
+      <x:c r="R62" s="119" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="S62" s="120" t="n">
+        <x:v>0.04947229551451187</x:v>
+      </x:c>
+      <x:c r="T62" s="120" t="n">
+        <x:v>0.37</x:v>
+      </x:c>
+      <x:c r="U62" s="120" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V62" s="120" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="117" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="B63" s="118" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="C63" s="119" t="n">
+        <x:v>6994</x:v>
+      </x:c>
+      <x:c r="D63" s="119" t="n">
+        <x:v>5554</x:v>
+      </x:c>
+      <x:c r="E63" s="119" t="n">
+        <x:v>1208</x:v>
+      </x:c>
+      <x:c r="F63" s="120" t="n">
+        <x:v>0.17271947383471548</x:v>
+      </x:c>
+      <x:c r="G63" s="120" t="n">
+        <x:v>0.27966101694915246</x:v>
+      </x:c>
+      <x:c r="H63" s="119" t="n">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="I63" s="120" t="n">
+        <x:v>0.36009933774834435</x:v>
+      </x:c>
+      <x:c r="J63" s="119" t="n">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="K63" s="120" t="n">
+        <x:v>0.10016556291390728</x:v>
+      </x:c>
+      <x:c r="L63" s="119" t="n">
+        <x:v>652</x:v>
+      </x:c>
+      <x:c r="M63" s="120" t="n">
+        <x:v>0.5397350993377483</x:v>
+      </x:c>
+      <x:c r="N63" s="119" t="n">
+        <x:v>809</x:v>
+      </x:c>
+      <x:c r="O63" s="120" t="n">
+        <x:v>0.6697019867549668</x:v>
+      </x:c>
+      <x:c r="P63" s="119" t="n">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="Q63" s="120" t="n">
+        <x:v>0.27980132450331124</x:v>
+      </x:c>
+      <x:c r="R63" s="119" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="S63" s="120" t="n">
+        <x:v>0.050496688741721855</x:v>
+      </x:c>
+      <x:c r="T63" s="120" t="n">
+        <x:v>0.31</x:v>
+      </x:c>
+      <x:c r="U63" s="120" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="V63" s="120" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="117" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="B64" s="118" t="str">
+        <x:v>Digital Partner</x:v>
+      </x:c>
+      <x:c r="C64" s="119" t="n">
+        <x:v>5371</x:v>
+      </x:c>
+      <x:c r="D64" s="119" t="n">
+        <x:v>4141</x:v>
+      </x:c>
+      <x:c r="E64" s="119" t="n">
+        <x:v>1018</x:v>
+      </x:c>
+      <x:c r="F64" s="120" t="n">
+        <x:v>0.18953639918078571</x:v>
+      </x:c>
+      <x:c r="G64" s="120" t="n">
+        <x:v>0.29024081115335876</x:v>
+      </x:c>
+      <x:c r="H64" s="119" t="n">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="I64" s="120" t="n">
+        <x:v>0.33988212180746563</x:v>
+      </x:c>
+      <x:c r="J64" s="119" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K64" s="120" t="n">
+        <x:v>0.09037328094302555</x:v>
+      </x:c>
+      <x:c r="L64" s="119" t="n">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="M64" s="120" t="n">
+        <x:v>0.5697445972495089</x:v>
+      </x:c>
+      <x:c r="N64" s="119" t="n">
+        <x:v>713</x:v>
+      </x:c>
+      <x:c r="O64" s="120" t="n">
+        <x:v>0.7003929273084479</x:v>
+      </x:c>
+      <x:c r="P64" s="119" t="n">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="Q64" s="120" t="n">
+        <x:v>0.24950884086444008</x:v>
+      </x:c>
+      <x:c r="R64" s="119" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="S64" s="120" t="n">
+        <x:v>0.05009823182711198</x:v>
+      </x:c>
+      <x:c r="T64" s="120" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="U64" s="120" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V64" s="120" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="117" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="B65" s="118" t="str">
+        <x:v>Inbound</x:v>
+      </x:c>
+      <x:c r="C65" s="119" t="n">
+        <x:v>6608</x:v>
+      </x:c>
+      <x:c r="D65" s="119" t="n">
+        <x:v>5145</x:v>
+      </x:c>
+      <x:c r="E65" s="119" t="n">
+        <x:v>1230</x:v>
+      </x:c>
+      <x:c r="F65" s="120" t="n">
+        <x:v>0.18613801452784504</x:v>
+      </x:c>
+      <x:c r="G65" s="120" t="n">
+        <x:v>0.3099041533546325</x:v>
+      </x:c>
+      <x:c r="H65" s="119" t="n">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="I65" s="120" t="n">
+        <x:v>0.3300813008130081</x:v>
+      </x:c>
+      <x:c r="J65" s="119" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="K65" s="120" t="n">
+        <x:v>0.09024390243902439</x:v>
+      </x:c>
+      <x:c r="L65" s="119" t="n">
+        <x:v>713</x:v>
+      </x:c>
+      <x:c r="M65" s="120" t="n">
+        <x:v>0.5796747967479675</x:v>
+      </x:c>
+      <x:c r="N65" s="119" t="n">
+        <x:v>873</x:v>
+      </x:c>
+      <x:c r="O65" s="120" t="n">
+        <x:v>0.7097560975609756</x:v>
+      </x:c>
+      <x:c r="P65" s="119" t="n">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="Q65" s="120" t="n">
+        <x:v>0.23983739837398374</x:v>
+      </x:c>
+      <x:c r="R65" s="119" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="S65" s="120" t="n">
+        <x:v>0.05040650406504065</x:v>
+      </x:c>
+      <x:c r="T65" s="120" t="n">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="U65" s="120" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V65" s="120" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="117" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="B66" s="118" t="str">
+        <x:v>Indirect</x:v>
+      </x:c>
+      <x:c r="C66" s="119" t="n">
+        <x:v>4598</x:v>
+      </x:c>
+      <x:c r="D66" s="119" t="n">
+        <x:v>3509</x:v>
+      </x:c>
+      <x:c r="E66" s="119" t="n">
+        <x:v>888</x:v>
+      </x:c>
+      <x:c r="F66" s="120" t="n">
+        <x:v>0.19312744671596346</x:v>
+      </x:c>
+      <x:c r="G66" s="120" t="n">
+        <x:v>0.30014641288433386</x:v>
+      </x:c>
+      <x:c r="H66" s="119" t="n">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="I66" s="120" t="n">
+        <x:v>0.3502252252252252</x:v>
+      </x:c>
+      <x:c r="J66" s="119" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K66" s="120" t="n">
+        <x:v>0.09009009009009009</x:v>
+      </x:c>
+      <x:c r="L66" s="119" t="n">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="M66" s="120" t="n">
+        <x:v>0.5596846846846847</x:v>
+      </x:c>
+      <x:c r="N66" s="119" t="n">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="O66" s="120" t="n">
+        <x:v>0.6903153153153153</x:v>
+      </x:c>
+      <x:c r="P66" s="119" t="n">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="Q66" s="120" t="n">
+        <x:v>0.26013513513513514</x:v>
+      </x:c>
+      <x:c r="R66" s="119" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="S66" s="120" t="n">
+        <x:v>0.04954954954954955</x:v>
+      </x:c>
+      <x:c r="T66" s="120" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="U66" s="120" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="V66" s="120" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="117" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="B67" s="118" t="str">
+        <x:v>OBTM</x:v>
+      </x:c>
+      <x:c r="C67" s="119" t="n">
+        <x:v>4250</x:v>
+      </x:c>
+      <x:c r="D67" s="119" t="n">
+        <x:v>3277</x:v>
+      </x:c>
+      <x:c r="E67" s="119" t="n">
+        <x:v>778</x:v>
+      </x:c>
+      <x:c r="F67" s="120" t="n">
+        <x:v>0.18305882352941177</x:v>
+      </x:c>
+      <x:c r="G67" s="120" t="n">
+        <x:v>0.269168026101142</x:v>
+      </x:c>
+      <x:c r="H67" s="119" t="n">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="I67" s="120" t="n">
+        <x:v>0.34061696658097684</x:v>
+      </x:c>
+      <x:c r="J67" s="119" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="K67" s="120" t="n">
+        <x:v>0.08997429305912596</x:v>
+      </x:c>
+      <x:c r="L67" s="119" t="n">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="M67" s="120" t="n">
+        <x:v>0.5694087403598972</x:v>
+      </x:c>
+      <x:c r="N67" s="119" t="n">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="O67" s="120" t="n">
+        <x:v>0.7005141388174807</x:v>
+      </x:c>
+      <x:c r="P67" s="119" t="n">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="Q67" s="120" t="n">
+        <x:v>0.2493573264781491</x:v>
+      </x:c>
+      <x:c r="R67" s="119" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="S67" s="120" t="n">
+        <x:v>0.05012853470437018</x:v>
+      </x:c>
+      <x:c r="T67" s="120" t="n">
+        <x:v>0.34</x:v>
+      </x:c>
+      <x:c r="U67" s="120" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V67" s="120" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="117" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="B68" s="118" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="C68" s="119" t="n">
+        <x:v>3014</x:v>
+      </x:c>
+      <x:c r="D68" s="119" t="n">
+        <x:v>2277</x:v>
+      </x:c>
+      <x:c r="E68" s="119" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="F68" s="120" t="n">
+        <x:v>0.19907100199071</x:v>
+      </x:c>
+      <x:c r="G68" s="120" t="n">
+        <x:v>0.33037694013303764</x:v>
+      </x:c>
+      <x:c r="H68" s="119" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="I68" s="120" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="J68" s="119" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K68" s="120" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="L68" s="119" t="n">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="M68" s="120" t="n">
+        <x:v>0.56</x:v>
+      </x:c>
+      <x:c r="N68" s="119" t="n">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="O68" s="120" t="n">
+        <x:v>0.69</x:v>
+      </x:c>
+      <x:c r="P68" s="119" t="n">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="Q68" s="120" t="n">
+        <x:v>0.26</x:v>
+      </x:c>
+      <x:c r="R68" s="119" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="S68" s="120" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="T68" s="120" t="n">
+        <x:v>0.32</x:v>
+      </x:c>
+      <x:c r="U68" s="120" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="V68" s="120" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:V2"/>
+    <x:mergeCell ref="A3:V3"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="19" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="10" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="24" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="20" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="B1" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="C1" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="D1" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="E1" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="F1" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="G1" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="H1" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="I1" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="J1" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="K1" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="L1" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="M1" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="27" customHeight="1">
+      <x:c r="A2" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="B2" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="C2" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="D2" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="E2" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="F2" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="G2" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="H2" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="I2" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="J2" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="K2" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="L2" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+      <x:c r="M2" s="109" t="str">
+        <x:v>September 2026 Channel Comparison</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="112" t="str">
+        <x:v>Scenario 2 deliberately shows broad channel deterioration; no single channel explains the +30% portfolio cancellation increase.</x:v>
+      </x:c>
+      <x:c r="B3" s="112" t="str">
+        <x:v>Scenario 2 deliberately shows broad channel deterioration; no single channel explains the +30% portfolio cancellation increase.</x:v>
+      </x:c>
+      <x:c r="C3" s="112" t="str">
+        <x:v>Scenario 2 deliberately shows broad channel deterioration; no single channel explains the +30% portfolio cancellation increase.</x:v>
+      </x:c>
+      <x:c r="D3" s="112" t="str">
+        <x:v>Scenario 2 deliberately shows broad channel deterioration; no single channel explains the +30% portfolio cancellation increase.</x:v>
+      </x:c>
+      <x:c r="E3" s="112" t="str">
+        <x:v>Scenario 2 deliberately shows broad channel deterioration; no single channel explains the +30% portfolio cancellation increase.</x:v>
+      </x:c>
+      <x:c r="F3" s="112" t="str">
+        <x:v>Scenario 2 deliberately shows broad channel deterioration; no single channel explains the +30% portfolio cancellation increase.</x:v>
+      </x:c>
+      <x:c r="G3" s="112" t="str">
+        <x:v>Scenario 2 deliberately shows broad channel deterioration; no single channel explains the +30% portfolio cancellation increase.</x:v>
+      </x:c>
+      <x:c r="H3" s="112" t="str">
+        <x:v>Scenario 2 deliberately shows broad channel deterioration; no single channel explains the +30% portfolio cancellation increase.</x:v>
+      </x:c>
+      <x:c r="I3" s="112" t="str">
+        <x:v>Scenario 2 deliberately shows broad channel deterioration; no single channel explains the +30% portfolio cancellation increase.</x:v>
+      </x:c>
+      <x:c r="J3" s="112" t="str">
+        <x:v>Scenario 2 deliberately shows broad channel deterioration; no single channel explains the +30% portfolio cancellation increase.</x:v>
+      </x:c>
+      <x:c r="K3" s="112" t="str">
+        <x:v>Scenario 2 deliberately shows broad channel deterioration; no single channel explains the +30% portfolio cancellation increase.</x:v>
+      </x:c>
+      <x:c r="L3" s="112" t="str">
+        <x:v>Scenario 2 deliberately shows broad channel deterioration; no single channel explains the +30% portfolio cancellation increase.</x:v>
+      </x:c>
+      <x:c r="M3" s="112" t="str">
+        <x:v>Scenario 2 deliberately shows broad channel deterioration; no single channel explains the +30% portfolio cancellation increase.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="116" t="str">
+        <x:v>Channel</x:v>
+      </x:c>
+      <x:c r="B5" s="116" t="str">
+        <x:v>Unique Sales</x:v>
+      </x:c>
+      <x:c r="C5" s="116" t="str">
+        <x:v>Installs</x:v>
+      </x:c>
+      <x:c r="D5" s="116" t="str">
+        <x:v>Cancellations</x:v>
+      </x:c>
+      <x:c r="E5" s="116" t="str">
+        <x:v>Cancel Rate</x:v>
+      </x:c>
+      <x:c r="F5" s="116" t="str">
+        <x:v>Cancel Growth vs Aug</x:v>
+      </x:c>
+      <x:c r="G5" s="116" t="str">
+        <x:v>Pre-ODD %</x:v>
+      </x:c>
+      <x:c r="H5" s="116" t="str">
+        <x:v>On-ODD %</x:v>
+      </x:c>
+      <x:c r="I5" s="116" t="str">
+        <x:v>Post-ODD %</x:v>
+      </x:c>
+      <x:c r="J5" s="116" t="str">
+        <x:v>Customer Miss %</x:v>
+      </x:c>
+      <x:c r="K5" s="116" t="str">
+        <x:v>Pending Customer Contact %</x:v>
+      </x:c>
+      <x:c r="L5" s="116" t="str">
+        <x:v>Install in Jeopardy %</x:v>
+      </x:c>
+      <x:c r="M5" s="116" t="str">
+        <x:v>On-Time Install %</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="121" t="str">
+        <x:v>D2D</x:v>
+      </x:c>
+      <x:c r="B6" s="122" t="n">
+        <x:v>7805</x:v>
+      </x:c>
+      <x:c r="C6" s="122" t="n">
+        <x:v>5897</x:v>
+      </x:c>
+      <x:c r="D6" s="122" t="n">
+        <x:v>1516</x:v>
+      </x:c>
+      <x:c r="E6" s="123" t="n">
+        <x:v>0.194234465086483</x:v>
+      </x:c>
+      <x:c r="F6" s="123" t="n">
+        <x:v>0.31940818102698</x:v>
+      </x:c>
+      <x:c r="G6" s="123" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="H6" s="123" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="I6" s="123" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="J6" s="123" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="K6" s="123" t="n">
+        <x:v>0.37</x:v>
+      </x:c>
+      <x:c r="L6" s="123" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="M6" s="123" t="n">
+        <x:v>0.76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="121" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="B7" s="122" t="n">
+        <x:v>6994</x:v>
+      </x:c>
+      <x:c r="C7" s="122" t="n">
+        <x:v>5554</x:v>
+      </x:c>
+      <x:c r="D7" s="122" t="n">
+        <x:v>1208</x:v>
+      </x:c>
+      <x:c r="E7" s="123" t="n">
+        <x:v>0.17271947383471548</x:v>
+      </x:c>
+      <x:c r="F7" s="123" t="n">
+        <x:v>0.27966101694915246</x:v>
+      </x:c>
+      <x:c r="G7" s="123" t="n">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="H7" s="123" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I7" s="123" t="n">
+        <x:v>0.54</x:v>
+      </x:c>
+      <x:c r="J7" s="123" t="n">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="K7" s="123" t="n">
+        <x:v>0.31</x:v>
+      </x:c>
+      <x:c r="L7" s="123" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M7" s="123" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="121" t="str">
+        <x:v>Digital Partner</x:v>
+      </x:c>
+      <x:c r="B8" s="122" t="n">
+        <x:v>5371</x:v>
+      </x:c>
+      <x:c r="C8" s="122" t="n">
+        <x:v>4141</x:v>
+      </x:c>
+      <x:c r="D8" s="122" t="n">
+        <x:v>1018</x:v>
+      </x:c>
+      <x:c r="E8" s="123" t="n">
+        <x:v>0.18953639918078571</x:v>
+      </x:c>
+      <x:c r="F8" s="123" t="n">
+        <x:v>0.29024081115335876</x:v>
+      </x:c>
+      <x:c r="G8" s="123" t="n">
+        <x:v>0.34</x:v>
+      </x:c>
+      <x:c r="H8" s="123" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="I8" s="123" t="n">
+        <x:v>0.57</x:v>
+      </x:c>
+      <x:c r="J8" s="123" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="K8" s="123" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="L8" s="123" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="M8" s="123" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="121" t="str">
+        <x:v>Inbound</x:v>
+      </x:c>
+      <x:c r="B9" s="122" t="n">
+        <x:v>6608</x:v>
+      </x:c>
+      <x:c r="C9" s="122" t="n">
+        <x:v>5145</x:v>
+      </x:c>
+      <x:c r="D9" s="122" t="n">
+        <x:v>1230</x:v>
+      </x:c>
+      <x:c r="E9" s="123" t="n">
+        <x:v>0.18613801452784504</x:v>
+      </x:c>
+      <x:c r="F9" s="123" t="n">
+        <x:v>0.3099041533546325</x:v>
+      </x:c>
+      <x:c r="G9" s="123" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="H9" s="123" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="I9" s="123" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="J9" s="123" t="n">
+        <x:v>0.71</x:v>
+      </x:c>
+      <x:c r="K9" s="123" t="n">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="L9" s="123" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="M9" s="123" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="121" t="str">
+        <x:v>Indirect</x:v>
+      </x:c>
+      <x:c r="B10" s="122" t="n">
+        <x:v>4598</x:v>
+      </x:c>
+      <x:c r="C10" s="122" t="n">
+        <x:v>3509</x:v>
+      </x:c>
+      <x:c r="D10" s="122" t="n">
+        <x:v>888</x:v>
+      </x:c>
+      <x:c r="E10" s="123" t="n">
+        <x:v>0.19312744671596346</x:v>
+      </x:c>
+      <x:c r="F10" s="123" t="n">
+        <x:v>0.30014641288433386</x:v>
+      </x:c>
+      <x:c r="G10" s="123" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="H10" s="123" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="I10" s="123" t="n">
+        <x:v>0.56</x:v>
+      </x:c>
+      <x:c r="J10" s="123" t="n">
+        <x:v>0.69</x:v>
+      </x:c>
+      <x:c r="K10" s="123" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="L10" s="123" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="M10" s="123" t="n">
+        <x:v>0.77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="121" t="str">
+        <x:v>OBTM</x:v>
+      </x:c>
+      <x:c r="B11" s="122" t="n">
+        <x:v>4250</x:v>
+      </x:c>
+      <x:c r="C11" s="122" t="n">
+        <x:v>3277</x:v>
+      </x:c>
+      <x:c r="D11" s="122" t="n">
+        <x:v>778</x:v>
+      </x:c>
+      <x:c r="E11" s="123" t="n">
+        <x:v>0.18305882352941177</x:v>
+      </x:c>
+      <x:c r="F11" s="123" t="n">
+        <x:v>0.269168026101142</x:v>
+      </x:c>
+      <x:c r="G11" s="123" t="n">
+        <x:v>0.34</x:v>
+      </x:c>
+      <x:c r="H11" s="123" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="I11" s="123" t="n">
+        <x:v>0.57</x:v>
+      </x:c>
+      <x:c r="J11" s="123" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="K11" s="123" t="n">
+        <x:v>0.34</x:v>
+      </x:c>
+      <x:c r="L11" s="123" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="M11" s="123" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="121" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B12" s="122" t="n">
+        <x:v>3014</x:v>
+      </x:c>
+      <x:c r="C12" s="122" t="n">
+        <x:v>2277</x:v>
+      </x:c>
+      <x:c r="D12" s="122" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="E12" s="123" t="n">
+        <x:v>0.19907100199071</x:v>
+      </x:c>
+      <x:c r="F12" s="123" t="n">
+        <x:v>0.33037694013303764</x:v>
+      </x:c>
+      <x:c r="G12" s="123" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="H12" s="123" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="I12" s="123" t="n">
+        <x:v>0.56</x:v>
+      </x:c>
+      <x:c r="J12" s="123" t="n">
+        <x:v>0.69</x:v>
+      </x:c>
+      <x:c r="K12" s="123" t="n">
+        <x:v>0.32</x:v>
+      </x:c>
+      <x:c r="L12" s="123" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="M12" s="123" t="n">
+        <x:v>0.76</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:M2"/>
+    <x:mergeCell ref="A3:M3"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="19" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="42" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+      <x:c r="B1" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+      <x:c r="C1" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+      <x:c r="D1" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+      <x:c r="E1" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+      <x:c r="F1" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+      <x:c r="G1" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+      <x:c r="H1" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+      <x:c r="I1" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+      <x:c r="J1" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="27" customHeight="1">
+      <x:c r="A2" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+      <x:c r="B2" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+      <x:c r="C2" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+      <x:c r="D2" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+      <x:c r="E2" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+      <x:c r="F2" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+      <x:c r="G2" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+      <x:c r="H2" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+      <x:c r="I2" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+      <x:c r="J2" s="109" t="str">
+        <x:v>September 2026 — State × Channel Drill</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="112" t="str">
+        <x:v>Supports app drill-down from a state into channel performance. North Carolina remains the hotspot across channels rather than one isolated sales source.</x:v>
+      </x:c>
+      <x:c r="B3" s="112" t="str">
+        <x:v>Supports app drill-down from a state into channel performance. North Carolina remains the hotspot across channels rather than one isolated sales source.</x:v>
+      </x:c>
+      <x:c r="C3" s="112" t="str">
+        <x:v>Supports app drill-down from a state into channel performance. North Carolina remains the hotspot across channels rather than one isolated sales source.</x:v>
+      </x:c>
+      <x:c r="D3" s="112" t="str">
+        <x:v>Supports app drill-down from a state into channel performance. North Carolina remains the hotspot across channels rather than one isolated sales source.</x:v>
+      </x:c>
+      <x:c r="E3" s="112" t="str">
+        <x:v>Supports app drill-down from a state into channel performance. North Carolina remains the hotspot across channels rather than one isolated sales source.</x:v>
+      </x:c>
+      <x:c r="F3" s="112" t="str">
+        <x:v>Supports app drill-down from a state into channel performance. North Carolina remains the hotspot across channels rather than one isolated sales source.</x:v>
+      </x:c>
+      <x:c r="G3" s="112" t="str">
+        <x:v>Supports app drill-down from a state into channel performance. North Carolina remains the hotspot across channels rather than one isolated sales source.</x:v>
+      </x:c>
+      <x:c r="H3" s="112" t="str">
+        <x:v>Supports app drill-down from a state into channel performance. North Carolina remains the hotspot across channels rather than one isolated sales source.</x:v>
+      </x:c>
+      <x:c r="I3" s="112" t="str">
+        <x:v>Supports app drill-down from a state into channel performance. North Carolina remains the hotspot across channels rather than one isolated sales source.</x:v>
+      </x:c>
+      <x:c r="J3" s="112" t="str">
+        <x:v>Supports app drill-down from a state into channel performance. North Carolina remains the hotspot across channels rather than one isolated sales source.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="116" t="str">
+        <x:v>State</x:v>
+      </x:c>
+      <x:c r="B5" s="116" t="str">
+        <x:v>Channel</x:v>
+      </x:c>
+      <x:c r="C5" s="116" t="str">
+        <x:v>Unique Sales</x:v>
+      </x:c>
+      <x:c r="D5" s="116" t="str">
+        <x:v>Installs</x:v>
+      </x:c>
+      <x:c r="E5" s="116" t="str">
+        <x:v>Cancellations</x:v>
+      </x:c>
+      <x:c r="F5" s="116" t="str">
+        <x:v>Cancel Rate</x:v>
+      </x:c>
+      <x:c r="G5" s="116" t="str">
+        <x:v>Post-ODD %</x:v>
+      </x:c>
+      <x:c r="H5" s="116" t="str">
+        <x:v>Customer Miss %</x:v>
+      </x:c>
+      <x:c r="I5" s="116" t="str">
+        <x:v>Pending Customer Contact %</x:v>
+      </x:c>
+      <x:c r="J5" s="116" t="str">
+        <x:v>Story</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="30" t="str">
+        <x:v>Michigan</x:v>
+      </x:c>
+      <x:c r="B6" s="30" t="str">
+        <x:v>D2D</x:v>
+      </x:c>
+      <x:c r="C6" s="64" t="n">
+        <x:v>1386</x:v>
+      </x:c>
+      <x:c r="D6" s="64" t="n">
+        <x:v>1073</x:v>
+      </x:c>
+      <x:c r="E6" s="64" t="n">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="F6" s="66" t="n">
+        <x:v>0.19336219336219337</x:v>
+      </x:c>
+      <x:c r="G6" s="66" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="H6" s="66" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="I6" s="66" t="n">
+        <x:v>0.37</x:v>
+      </x:c>
+      <x:c r="J6" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="30" t="str">
+        <x:v>Michigan</x:v>
+      </x:c>
+      <x:c r="B7" s="30" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="C7" s="64" t="n">
+        <x:v>1247</x:v>
+      </x:c>
+      <x:c r="D7" s="64" t="n">
+        <x:v>1014</x:v>
+      </x:c>
+      <x:c r="E7" s="64" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="F7" s="66" t="n">
+        <x:v>0.1764234161988773</x:v>
+      </x:c>
+      <x:c r="G7" s="66" t="n">
+        <x:v>0.54</x:v>
+      </x:c>
+      <x:c r="H7" s="66" t="n">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="I7" s="66" t="n">
+        <x:v>0.31</x:v>
+      </x:c>
+      <x:c r="J7" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="30" t="str">
+        <x:v>Michigan</x:v>
+      </x:c>
+      <x:c r="B8" s="30" t="str">
+        <x:v>Digital Partner</x:v>
+      </x:c>
+      <x:c r="C8" s="64" t="n">
+        <x:v>970</x:v>
+      </x:c>
+      <x:c r="D8" s="64" t="n">
+        <x:v>766</x:v>
+      </x:c>
+      <x:c r="E8" s="64" t="n">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="F8" s="66" t="n">
+        <x:v>0.18969072164948453</x:v>
+      </x:c>
+      <x:c r="G8" s="66" t="n">
+        <x:v>0.57</x:v>
+      </x:c>
+      <x:c r="H8" s="66" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I8" s="66" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="J8" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="30" t="str">
+        <x:v>Michigan</x:v>
+      </x:c>
+      <x:c r="B9" s="30" t="str">
+        <x:v>Inbound</x:v>
+      </x:c>
+      <x:c r="C9" s="64" t="n">
+        <x:v>1178</x:v>
+      </x:c>
+      <x:c r="D9" s="64" t="n">
+        <x:v>940</x:v>
+      </x:c>
+      <x:c r="E9" s="64" t="n">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="F9" s="66" t="n">
+        <x:v>0.18590831918505943</x:v>
+      </x:c>
+      <x:c r="G9" s="66" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="H9" s="66" t="n">
+        <x:v>0.71</x:v>
+      </x:c>
+      <x:c r="I9" s="66" t="n">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="J9" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="30" t="str">
+        <x:v>Michigan</x:v>
+      </x:c>
+      <x:c r="B10" s="30" t="str">
+        <x:v>Indirect</x:v>
+      </x:c>
+      <x:c r="C10" s="64" t="n">
+        <x:v>832</x:v>
+      </x:c>
+      <x:c r="D10" s="64" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="E10" s="64" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F10" s="66" t="n">
+        <x:v>0.19230769230769232</x:v>
+      </x:c>
+      <x:c r="G10" s="66" t="n">
+        <x:v>0.56</x:v>
+      </x:c>
+      <x:c r="H10" s="66" t="n">
+        <x:v>0.69</x:v>
+      </x:c>
+      <x:c r="I10" s="66" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="J10" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="30" t="str">
+        <x:v>Michigan</x:v>
+      </x:c>
+      <x:c r="B11" s="30" t="str">
+        <x:v>OBTM</x:v>
+      </x:c>
+      <x:c r="C11" s="64" t="n">
+        <x:v>762</x:v>
+      </x:c>
+      <x:c r="D11" s="64" t="n">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="E11" s="64" t="n">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="F11" s="66" t="n">
+        <x:v>0.18766404199475065</x:v>
+      </x:c>
+      <x:c r="G11" s="66" t="n">
+        <x:v>0.57</x:v>
+      </x:c>
+      <x:c r="H11" s="66" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I11" s="66" t="n">
+        <x:v>0.34</x:v>
+      </x:c>
+      <x:c r="J11" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="30" t="str">
+        <x:v>Michigan</x:v>
+      </x:c>
+      <x:c r="B12" s="30" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="C12" s="64" t="n">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="D12" s="64" t="n">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="E12" s="64" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F12" s="66" t="n">
+        <x:v>0.19099099099099098</x:v>
+      </x:c>
+      <x:c r="G12" s="66" t="n">
+        <x:v>0.56</x:v>
+      </x:c>
+      <x:c r="H12" s="66" t="n">
+        <x:v>0.69</x:v>
+      </x:c>
+      <x:c r="I12" s="66" t="n">
+        <x:v>0.32</x:v>
+      </x:c>
+      <x:c r="J12" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="30" t="str">
+        <x:v>Missouri</x:v>
+      </x:c>
+      <x:c r="B13" s="30" t="str">
+        <x:v>D2D</x:v>
+      </x:c>
+      <x:c r="C13" s="64" t="n">
+        <x:v>1090</x:v>
+      </x:c>
+      <x:c r="D13" s="64" t="n">
+        <x:v>833</x:v>
+      </x:c>
+      <x:c r="E13" s="64" t="n">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="F13" s="66" t="n">
+        <x:v>0.19174311926605506</x:v>
+      </x:c>
+      <x:c r="G13" s="66" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="H13" s="66" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="I13" s="66" t="n">
+        <x:v>0.37</x:v>
+      </x:c>
+      <x:c r="J13" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="30" t="str">
+        <x:v>Missouri</x:v>
+      </x:c>
+      <x:c r="B14" s="30" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="C14" s="64" t="n">
+        <x:v>981</x:v>
+      </x:c>
+      <x:c r="D14" s="64" t="n">
+        <x:v>788</x:v>
+      </x:c>
+      <x:c r="E14" s="64" t="n">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="F14" s="66" t="n">
+        <x:v>0.1743119266055046</x:v>
+      </x:c>
+      <x:c r="G14" s="66" t="n">
+        <x:v>0.54</x:v>
+      </x:c>
+      <x:c r="H14" s="66" t="n">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="I14" s="66" t="n">
+        <x:v>0.31</x:v>
+      </x:c>
+      <x:c r="J14" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="30" t="str">
+        <x:v>Missouri</x:v>
+      </x:c>
+      <x:c r="B15" s="30" t="str">
+        <x:v>Digital Partner</x:v>
+      </x:c>
+      <x:c r="C15" s="64" t="n">
+        <x:v>763</x:v>
+      </x:c>
+      <x:c r="D15" s="64" t="n">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="E15" s="64" t="n">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="F15" s="66" t="n">
+        <x:v>0.1874180865006553</x:v>
+      </x:c>
+      <x:c r="G15" s="66" t="n">
+        <x:v>0.57</x:v>
+      </x:c>
+      <x:c r="H15" s="66" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I15" s="66" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="J15" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="30" t="str">
+        <x:v>Missouri</x:v>
+      </x:c>
+      <x:c r="B16" s="30" t="str">
+        <x:v>Inbound</x:v>
+      </x:c>
+      <x:c r="C16" s="64" t="n">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="D16" s="64" t="n">
+        <x:v>730</x:v>
+      </x:c>
+      <x:c r="E16" s="64" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="F16" s="66" t="n">
+        <x:v>0.18338727076591155</x:v>
+      </x:c>
+      <x:c r="G16" s="66" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="H16" s="66" t="n">
+        <x:v>0.71</x:v>
+      </x:c>
+      <x:c r="I16" s="66" t="n">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="J16" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="30" t="str">
+        <x:v>Missouri</x:v>
+      </x:c>
+      <x:c r="B17" s="30" t="str">
+        <x:v>Indirect</x:v>
+      </x:c>
+      <x:c r="C17" s="64" t="n">
+        <x:v>654</x:v>
+      </x:c>
+      <x:c r="D17" s="64" t="n">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="E17" s="64" t="n">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="F17" s="66" t="n">
+        <x:v>0.18960244648318042</x:v>
+      </x:c>
+      <x:c r="G17" s="66" t="n">
+        <x:v>0.56</x:v>
+      </x:c>
+      <x:c r="H17" s="66" t="n">
+        <x:v>0.69</x:v>
+      </x:c>
+      <x:c r="I17" s="66" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="J17" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="30" t="str">
+        <x:v>Missouri</x:v>
+      </x:c>
+      <x:c r="B18" s="30" t="str">
+        <x:v>OBTM</x:v>
+      </x:c>
+      <x:c r="C18" s="64" t="n">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="D18" s="64" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="E18" s="64" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F18" s="66" t="n">
+        <x:v>0.18530884808013356</x:v>
+      </x:c>
+      <x:c r="G18" s="66" t="n">
+        <x:v>0.57</x:v>
+      </x:c>
+      <x:c r="H18" s="66" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I18" s="66" t="n">
+        <x:v>0.34</x:v>
+      </x:c>
+      <x:c r="J18" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="30" t="str">
+        <x:v>Missouri</x:v>
+      </x:c>
+      <x:c r="B19" s="30" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="C19" s="64" t="n">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="D19" s="64" t="n">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="E19" s="64" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F19" s="66" t="n">
+        <x:v>0.18807339449541285</x:v>
+      </x:c>
+      <x:c r="G19" s="66" t="n">
+        <x:v>0.56</x:v>
+      </x:c>
+      <x:c r="H19" s="66" t="n">
+        <x:v>0.69</x:v>
+      </x:c>
+      <x:c r="I19" s="66" t="n">
+        <x:v>0.32</x:v>
+      </x:c>
+      <x:c r="J19" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="30" t="str">
+        <x:v>Mississippi</x:v>
+      </x:c>
+      <x:c r="B20" s="30" t="str">
+        <x:v>D2D</x:v>
+      </x:c>
+      <x:c r="C20" s="64" t="n">
+        <x:v>924</x:v>
+      </x:c>
+      <x:c r="D20" s="64" t="n">
+        <x:v>697</x:v>
+      </x:c>
+      <x:c r="E20" s="64" t="n">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="F20" s="66" t="n">
+        <x:v>0.19155844155844157</x:v>
+      </x:c>
+      <x:c r="G20" s="66" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="H20" s="66" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="I20" s="66" t="n">
+        <x:v>0.37</x:v>
+      </x:c>
+      <x:c r="J20" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="30" t="str">
+        <x:v>Mississippi</x:v>
+      </x:c>
+      <x:c r="B21" s="30" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="C21" s="64" t="n">
+        <x:v>832</x:v>
+      </x:c>
+      <x:c r="D21" s="64" t="n">
+        <x:v>660</x:v>
+      </x:c>
+      <x:c r="E21" s="64" t="n">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="F21" s="66" t="n">
+        <x:v>0.17548076923076922</x:v>
+      </x:c>
+      <x:c r="G21" s="66" t="n">
+        <x:v>0.54</x:v>
+      </x:c>
+      <x:c r="H21" s="66" t="n">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="I21" s="66" t="n">
+        <x:v>0.31</x:v>
+      </x:c>
+      <x:c r="J21" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="30" t="str">
+        <x:v>Mississippi</x:v>
+      </x:c>
+      <x:c r="B22" s="30" t="str">
+        <x:v>Digital Partner</x:v>
+      </x:c>
+      <x:c r="C22" s="64" t="n">
+        <x:v>647</x:v>
+      </x:c>
+      <x:c r="D22" s="64" t="n">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="E22" s="64" t="n">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F22" s="66" t="n">
+        <x:v>0.18856259659969088</x:v>
+      </x:c>
+      <x:c r="G22" s="66" t="n">
+        <x:v>0.57</x:v>
+      </x:c>
+      <x:c r="H22" s="66" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I22" s="66" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="J22" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="30" t="str">
+        <x:v>Mississippi</x:v>
+      </x:c>
+      <x:c r="B23" s="30" t="str">
+        <x:v>Inbound</x:v>
+      </x:c>
+      <x:c r="C23" s="64" t="n">
+        <x:v>785</x:v>
+      </x:c>
+      <x:c r="D23" s="64" t="n">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="E23" s="64" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F23" s="66" t="n">
+        <x:v>0.18471337579617833</x:v>
+      </x:c>
+      <x:c r="G23" s="66" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="H23" s="66" t="n">
+        <x:v>0.71</x:v>
+      </x:c>
+      <x:c r="I23" s="66" t="n">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="J23" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="30" t="str">
+        <x:v>Mississippi</x:v>
+      </x:c>
+      <x:c r="B24" s="30" t="str">
+        <x:v>Indirect</x:v>
+      </x:c>
+      <x:c r="C24" s="64" t="n">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="D24" s="64" t="n">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="E24" s="64" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F24" s="66" t="n">
+        <x:v>0.18953068592057762</x:v>
+      </x:c>
+      <x:c r="G24" s="66" t="n">
+        <x:v>0.56</x:v>
+      </x:c>
+      <x:c r="H24" s="66" t="n">
+        <x:v>0.69</x:v>
+      </x:c>
+      <x:c r="I24" s="66" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="J24" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="30" t="str">
+        <x:v>Mississippi</x:v>
+      </x:c>
+      <x:c r="B25" s="30" t="str">
+        <x:v>OBTM</x:v>
+      </x:c>
+      <x:c r="C25" s="64" t="n">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="D25" s="64" t="n">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="E25" s="64" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="F25" s="66" t="n">
+        <x:v>0.18700787401574803</x:v>
+      </x:c>
+      <x:c r="G25" s="66" t="n">
+        <x:v>0.57</x:v>
+      </x:c>
+      <x:c r="H25" s="66" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I25" s="66" t="n">
+        <x:v>0.34</x:v>
+      </x:c>
+      <x:c r="J25" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="30" t="str">
+        <x:v>Mississippi</x:v>
+      </x:c>
+      <x:c r="B26" s="30" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="C26" s="64" t="n">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="D26" s="64" t="n">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="E26" s="64" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F26" s="66" t="n">
+        <x:v>0.1891891891891892</x:v>
+      </x:c>
+      <x:c r="G26" s="66" t="n">
+        <x:v>0.56</x:v>
+      </x:c>
+      <x:c r="H26" s="66" t="n">
+        <x:v>0.69</x:v>
+      </x:c>
+      <x:c r="I26" s="66" t="n">
+        <x:v>0.32</x:v>
+      </x:c>
+      <x:c r="J26" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="127" t="str">
+        <x:v>North Carolina</x:v>
+      </x:c>
+      <x:c r="B27" s="127" t="str">
+        <x:v>D2D</x:v>
+      </x:c>
+      <x:c r="C27" s="128" t="n">
+        <x:v>2051</x:v>
+      </x:c>
+      <x:c r="D27" s="128" t="n">
+        <x:v>1447</x:v>
+      </x:c>
+      <x:c r="E27" s="128" t="n">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="F27" s="129" t="n">
+        <x:v>0.2052657240370551</x:v>
+      </x:c>
+      <x:c r="G27" s="129" t="n">
+        <x:v>0.6499999999999999</x:v>
+      </x:c>
+      <x:c r="H27" s="129" t="n">
+        <x:v>0.76</x:v>
+      </x:c>
+      <x:c r="I27" s="129" t="n">
+        <x:v>0.42</x:v>
+      </x:c>
+      <x:c r="J27" s="127" t="str">
+        <x:v>NC hotspot: broad Post-ODD / customer-contact deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="127" t="str">
+        <x:v>North Carolina</x:v>
+      </x:c>
+      <x:c r="B28" s="127" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="C28" s="128" t="n">
+        <x:v>1622</x:v>
+      </x:c>
+      <x:c r="D28" s="128" t="n">
+        <x:v>1203</x:v>
+      </x:c>
+      <x:c r="E28" s="128" t="n">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="F28" s="129" t="n">
+        <x:v>0.187422934648582</x:v>
+      </x:c>
+      <x:c r="G28" s="129" t="n">
+        <x:v>0.6100000000000001</x:v>
+      </x:c>
+      <x:c r="H28" s="129" t="n">
+        <x:v>0.7100000000000001</x:v>
+      </x:c>
+      <x:c r="I28" s="129" t="n">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="J28" s="127" t="str">
+        <x:v>NC hotspot: broad Post-ODD / customer-contact deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="127" t="str">
+        <x:v>North Carolina</x:v>
+      </x:c>
+      <x:c r="B29" s="127" t="str">
+        <x:v>Digital Partner</x:v>
+      </x:c>
+      <x:c r="C29" s="128" t="n">
+        <x:v>1288</x:v>
+      </x:c>
+      <x:c r="D29" s="128" t="n">
+        <x:v>928</x:v>
+      </x:c>
+      <x:c r="E29" s="128" t="n">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="F29" s="129" t="n">
+        <x:v>0.20108695652173914</x:v>
+      </x:c>
+      <x:c r="G29" s="129" t="n">
+        <x:v>0.6399999999999999</x:v>
+      </x:c>
+      <x:c r="H29" s="129" t="n">
+        <x:v>0.74</x:v>
+      </x:c>
+      <x:c r="I29" s="129" t="n">
+        <x:v>0.39999999999999997</x:v>
+      </x:c>
+      <x:c r="J29" s="127" t="str">
+        <x:v>NC hotspot: broad Post-ODD / customer-contact deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="127" t="str">
+        <x:v>North Carolina</x:v>
+      </x:c>
+      <x:c r="B30" s="127" t="str">
+        <x:v>Inbound</x:v>
+      </x:c>
+      <x:c r="C30" s="128" t="n">
+        <x:v>1717</x:v>
+      </x:c>
+      <x:c r="D30" s="128" t="n">
+        <x:v>1249</x:v>
+      </x:c>
+      <x:c r="E30" s="128" t="n">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="F30" s="129" t="n">
+        <x:v>0.19743739079790332</x:v>
+      </x:c>
+      <x:c r="G30" s="129" t="n">
+        <x:v>0.6499999999999999</x:v>
+      </x:c>
+      <x:c r="H30" s="129" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="I30" s="129" t="n">
+        <x:v>0.41</x:v>
+      </x:c>
+      <x:c r="J30" s="127" t="str">
+        <x:v>NC hotspot: broad Post-ODD / customer-contact deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="127" t="str">
+        <x:v>North Carolina</x:v>
+      </x:c>
+      <x:c r="B31" s="127" t="str">
+        <x:v>Indirect</x:v>
+      </x:c>
+      <x:c r="C31" s="128" t="n">
+        <x:v>1097</x:v>
+      </x:c>
+      <x:c r="D31" s="128" t="n">
+        <x:v>782</x:v>
+      </x:c>
+      <x:c r="E31" s="128" t="n">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="F31" s="129" t="n">
+        <x:v>0.203281677301732</x:v>
+      </x:c>
+      <x:c r="G31" s="129" t="n">
+        <x:v>0.6300000000000001</x:v>
+      </x:c>
+      <x:c r="H31" s="129" t="n">
+        <x:v>0.73</x:v>
+      </x:c>
+      <x:c r="I31" s="129" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="J31" s="127" t="str">
+        <x:v>NC hotspot: broad Post-ODD / customer-contact deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="127" t="str">
+        <x:v>North Carolina</x:v>
+      </x:c>
+      <x:c r="B32" s="127" t="str">
+        <x:v>OBTM</x:v>
+      </x:c>
+      <x:c r="C32" s="128" t="n">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="D32" s="128" t="n">
+        <x:v>722</x:v>
+      </x:c>
+      <x:c r="E32" s="128" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="F32" s="129" t="n">
+        <x:v>0.1996007984031936</x:v>
+      </x:c>
+      <x:c r="G32" s="129" t="n">
+        <x:v>0.6399999999999999</x:v>
+      </x:c>
+      <x:c r="H32" s="129" t="n">
+        <x:v>0.74</x:v>
+      </x:c>
+      <x:c r="I32" s="129" t="n">
+        <x:v>0.39</x:v>
+      </x:c>
+      <x:c r="J32" s="127" t="str">
+        <x:v>NC hotspot: broad Post-ODD / customer-contact deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="127" t="str">
+        <x:v>North Carolina</x:v>
+      </x:c>
+      <x:c r="B33" s="127" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="C33" s="128" t="n">
+        <x:v>763</x:v>
+      </x:c>
+      <x:c r="D33" s="128" t="n">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="E33" s="128" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="F33" s="129" t="n">
+        <x:v>0.2018348623853211</x:v>
+      </x:c>
+      <x:c r="G33" s="129" t="n">
+        <x:v>0.6300000000000001</x:v>
+      </x:c>
+      <x:c r="H33" s="129" t="n">
+        <x:v>0.73</x:v>
+      </x:c>
+      <x:c r="I33" s="129" t="n">
+        <x:v>0.37</x:v>
+      </x:c>
+      <x:c r="J33" s="127" t="str">
+        <x:v>NC hotspot: broad Post-ODD / customer-contact deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="30" t="str">
+        <x:v>New Jersey</x:v>
+      </x:c>
+      <x:c r="B34" s="30" t="str">
+        <x:v>D2D</x:v>
+      </x:c>
+      <x:c r="C34" s="64" t="n">
+        <x:v>890</x:v>
+      </x:c>
+      <x:c r="D34" s="64" t="n">
+        <x:v>706</x:v>
+      </x:c>
+      <x:c r="E34" s="64" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F34" s="66" t="n">
+        <x:v>0.16853932584269662</x:v>
+      </x:c>
+      <x:c r="G34" s="66" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="H34" s="66" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="I34" s="66" t="n">
+        <x:v>0.37</x:v>
+      </x:c>
+      <x:c r="J34" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="30" t="str">
+        <x:v>New Jersey</x:v>
+      </x:c>
+      <x:c r="B35" s="30" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="C35" s="64" t="n">
+        <x:v>801</x:v>
+      </x:c>
+      <x:c r="D35" s="64" t="n">
+        <x:v>668</x:v>
+      </x:c>
+      <x:c r="E35" s="64" t="n">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="F35" s="66" t="n">
+        <x:v>0.15480649188514356</x:v>
+      </x:c>
+      <x:c r="G35" s="66" t="n">
+        <x:v>0.54</x:v>
+      </x:c>
+      <x:c r="H35" s="66" t="n">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="I35" s="66" t="n">
+        <x:v>0.31</x:v>
+      </x:c>
+      <x:c r="J35" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="30" t="str">
+        <x:v>New Jersey</x:v>
+      </x:c>
+      <x:c r="B36" s="30" t="str">
+        <x:v>Digital Partner</x:v>
+      </x:c>
+      <x:c r="C36" s="64" t="n">
+        <x:v>623</x:v>
+      </x:c>
+      <x:c r="D36" s="64" t="n">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="E36" s="64" t="n">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F36" s="66" t="n">
+        <x:v>0.1653290529695024</x:v>
+      </x:c>
+      <x:c r="G36" s="66" t="n">
+        <x:v>0.57</x:v>
+      </x:c>
+      <x:c r="H36" s="66" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I36" s="66" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="J36" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="30" t="str">
+        <x:v>New Jersey</x:v>
+      </x:c>
+      <x:c r="B37" s="30" t="str">
+        <x:v>Inbound</x:v>
+      </x:c>
+      <x:c r="C37" s="64" t="n">
+        <x:v>757</x:v>
+      </x:c>
+      <x:c r="D37" s="64" t="n">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="E37" s="64" t="n">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F37" s="66" t="n">
+        <x:v>0.16248348745046234</x:v>
+      </x:c>
+      <x:c r="G37" s="66" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="H37" s="66" t="n">
+        <x:v>0.71</x:v>
+      </x:c>
+      <x:c r="I37" s="66" t="n">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="J37" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="30" t="str">
+        <x:v>New Jersey</x:v>
+      </x:c>
+      <x:c r="B38" s="30" t="str">
+        <x:v>Indirect</x:v>
+      </x:c>
+      <x:c r="C38" s="64" t="n">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="D38" s="64" t="n">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="E38" s="64" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F38" s="66" t="n">
+        <x:v>0.16666666666666666</x:v>
+      </x:c>
+      <x:c r="G38" s="66" t="n">
+        <x:v>0.56</x:v>
+      </x:c>
+      <x:c r="H38" s="66" t="n">
+        <x:v>0.69</x:v>
+      </x:c>
+      <x:c r="I38" s="66" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="J38" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="30" t="str">
+        <x:v>New Jersey</x:v>
+      </x:c>
+      <x:c r="B39" s="30" t="str">
+        <x:v>OBTM</x:v>
+      </x:c>
+      <x:c r="C39" s="64" t="n">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="D39" s="64" t="n">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="E39" s="64" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F39" s="66" t="n">
+        <x:v>0.16359918200409</x:v>
+      </x:c>
+      <x:c r="G39" s="66" t="n">
+        <x:v>0.57</x:v>
+      </x:c>
+      <x:c r="H39" s="66" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I39" s="66" t="n">
+        <x:v>0.34</x:v>
+      </x:c>
+      <x:c r="J39" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="30" t="str">
+        <x:v>New Jersey</x:v>
+      </x:c>
+      <x:c r="B40" s="30" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="C40" s="64" t="n">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="D40" s="64" t="n">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="E40" s="64" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F40" s="66" t="n">
+        <x:v>0.16573033707865167</x:v>
+      </x:c>
+      <x:c r="G40" s="66" t="n">
+        <x:v>0.56</x:v>
+      </x:c>
+      <x:c r="H40" s="66" t="n">
+        <x:v>0.69</x:v>
+      </x:c>
+      <x:c r="I40" s="66" t="n">
+        <x:v>0.32</x:v>
+      </x:c>
+      <x:c r="J40" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="30" t="str">
+        <x:v>Ohio</x:v>
+      </x:c>
+      <x:c r="B41" s="30" t="str">
+        <x:v>D2D</x:v>
+      </x:c>
+      <x:c r="C41" s="64" t="n">
+        <x:v>1530</x:v>
+      </x:c>
+      <x:c r="D41" s="64" t="n">
+        <x:v>1184</x:v>
+      </x:c>
+      <x:c r="E41" s="64" t="n">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="F41" s="66" t="n">
+        <x:v>0.19411764705882353</x:v>
+      </x:c>
+      <x:c r="G41" s="66" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="H41" s="66" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="I41" s="66" t="n">
+        <x:v>0.37</x:v>
+      </x:c>
+      <x:c r="J41" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="30" t="str">
+        <x:v>Ohio</x:v>
+      </x:c>
+      <x:c r="B42" s="30" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="C42" s="64" t="n">
+        <x:v>1377</x:v>
+      </x:c>
+      <x:c r="D42" s="64" t="n">
+        <x:v>1120</x:v>
+      </x:c>
+      <x:c r="E42" s="64" t="n">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="F42" s="66" t="n">
+        <x:v>0.17719680464778503</x:v>
+      </x:c>
+      <x:c r="G42" s="66" t="n">
+        <x:v>0.54</x:v>
+      </x:c>
+      <x:c r="H42" s="66" t="n">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="I42" s="66" t="n">
+        <x:v>0.31</x:v>
+      </x:c>
+      <x:c r="J42" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="30" t="str">
+        <x:v>Ohio</x:v>
+      </x:c>
+      <x:c r="B43" s="30" t="str">
+        <x:v>Digital Partner</x:v>
+      </x:c>
+      <x:c r="C43" s="64" t="n">
+        <x:v>1071</x:v>
+      </x:c>
+      <x:c r="D43" s="64" t="n">
+        <x:v>846</x:v>
+      </x:c>
+      <x:c r="E43" s="64" t="n">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="F43" s="66" t="n">
+        <x:v>0.19047619047619047</x:v>
+      </x:c>
+      <x:c r="G43" s="66" t="n">
+        <x:v>0.57</x:v>
+      </x:c>
+      <x:c r="H43" s="66" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I43" s="66" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="J43" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="30" t="str">
+        <x:v>Ohio</x:v>
+      </x:c>
+      <x:c r="B44" s="30" t="str">
+        <x:v>Inbound</x:v>
+      </x:c>
+      <x:c r="C44" s="64" t="n">
+        <x:v>1301</x:v>
+      </x:c>
+      <x:c r="D44" s="64" t="n">
+        <x:v>1038</x:v>
+      </x:c>
+      <x:c r="E44" s="64" t="n">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="F44" s="66" t="n">
+        <x:v>0.18677940046118371</x:v>
+      </x:c>
+      <x:c r="G44" s="66" t="n">
+        <x:v>0.58</x:v>
+      </x:c>
+      <x:c r="H44" s="66" t="n">
+        <x:v>0.71</x:v>
+      </x:c>
+      <x:c r="I44" s="66" t="n">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="J44" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="30" t="str">
+        <x:v>Ohio</x:v>
+      </x:c>
+      <x:c r="B45" s="30" t="str">
+        <x:v>Indirect</x:v>
+      </x:c>
+      <x:c r="C45" s="64" t="n">
+        <x:v>918</x:v>
+      </x:c>
+      <x:c r="D45" s="64" t="n">
+        <x:v>718</x:v>
+      </x:c>
+      <x:c r="E45" s="64" t="n">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="F45" s="66" t="n">
+        <x:v>0.19281045751633988</x:v>
+      </x:c>
+      <x:c r="G45" s="66" t="n">
+        <x:v>0.56</x:v>
+      </x:c>
+      <x:c r="H45" s="66" t="n">
+        <x:v>0.69</x:v>
+      </x:c>
+      <x:c r="I45" s="66" t="n">
+        <x:v>0.33</x:v>
+      </x:c>
+      <x:c r="J45" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="30" t="str">
+        <x:v>Ohio</x:v>
+      </x:c>
+      <x:c r="B46" s="30" t="str">
+        <x:v>OBTM</x:v>
+      </x:c>
+      <x:c r="C46" s="64" t="n">
+        <x:v>841</x:v>
+      </x:c>
+      <x:c r="D46" s="64" t="n">
+        <x:v>664</x:v>
+      </x:c>
+      <x:c r="E46" s="64" t="n">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="F46" s="66" t="n">
+        <x:v>0.18906064209274673</x:v>
+      </x:c>
+      <x:c r="G46" s="66" t="n">
+        <x:v>0.57</x:v>
+      </x:c>
+      <x:c r="H46" s="66" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="I46" s="66" t="n">
+        <x:v>0.34</x:v>
+      </x:c>
+      <x:c r="J46" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="30" t="str">
+        <x:v>Ohio</x:v>
+      </x:c>
+      <x:c r="B47" s="30" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="C47" s="64" t="n">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="D47" s="64" t="n">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="E47" s="64" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F47" s="66" t="n">
+        <x:v>0.1895424836601307</x:v>
+      </x:c>
+      <x:c r="G47" s="66" t="n">
+        <x:v>0.56</x:v>
+      </x:c>
+      <x:c r="H47" s="66" t="n">
+        <x:v>0.69</x:v>
+      </x:c>
+      <x:c r="I47" s="66" t="n">
+        <x:v>0.32</x:v>
+      </x:c>
+      <x:c r="J47" s="30" t="str">
+        <x:v>Broad September deterioration</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J2"/>
+    <x:mergeCell ref="A3:J3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2859,7 +9796,7 @@
     <x:mergeCell ref="A3:S3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fbe4be3016c4738"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5748debfeaff4ae6"/>
 </x:worksheet>
 </file>
 
